--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45357</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>46083</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>46097</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45603</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45134</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45675</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>45385</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45086</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>44512</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45299</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45621</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45895</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44768</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>46001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>46004</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>45236</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>45568</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>46073</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>46097</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>46109</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44553</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44971</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>46217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>46223</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45231</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45779</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45806</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45806</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45264</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45876</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>44498</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>44861</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44679</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44474</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6165,7 +6165,7 @@
         <v>44512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>44512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44533</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>44531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>44636</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44655</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44868</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44809</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44533</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>44713</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44497</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>44552</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>44491</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>44506</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>44462</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44732</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>44657</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44543</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>44854</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         <v>44776</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44775</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44655</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44852</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44656</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44733</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>44532</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44594</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44750</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44509</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>44868</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44663</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44882</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44621</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>44524</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44606</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44466</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44609</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44480</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44638</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44624</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>44609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44464</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44880</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44772</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45412</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>45180</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45348</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44460</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>44959</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45553</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>45163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44881</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45162</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44512</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45607</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>45585</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>45681</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45357</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44760</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45162</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44959</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>45211</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>45602</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44895</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44724</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44697</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44894</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44578</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45124</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45344</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44477</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>45314</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45070</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45201</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45558</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45321</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45247</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45357</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45606</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45237</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44959</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45376</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45363</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45691</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45265</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45181</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45227</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>44916</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44916</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45162</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45162</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45239</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45071</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45362</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45162</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45334</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45411</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45140</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45482</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45598</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45224</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44566</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44517</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>44929</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>44824</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45399</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45603</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45666</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45518</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45443</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44971</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>44970</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45683</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>45664</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45246</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>44896</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45621</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45685</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45299</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45043</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45324</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45180</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44947</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45157</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44873</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>45606</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44917</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45227</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>45227</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45412</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>45259</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>45608</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>44800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
         <v>44663</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>45231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45663</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44503</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>44663</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45075</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>44606</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45194</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>44607</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>44607</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45257</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44558</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45281</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>45281</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45281</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45191</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45659</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45553</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45553</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>45341</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45239</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>45343</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45361</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45002</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45735</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45112</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45593</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>45582</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45427</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>45324</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45324</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>44477</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45159</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>44638</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44638</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45797</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45889</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45889</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45889</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45252</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45795</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45889</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45354</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45895</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45233</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45085</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45085</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45484</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45343</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45895</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45895</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45089</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45643</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44636</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45835</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45187</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45244</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45611</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45362</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45896</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45245</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45896</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45636</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45547</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45547</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45547</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45075</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>44945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>45162</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45901</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45035</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44894</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45771</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45924</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45826</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45231</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45091</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45320</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45905</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45134</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>46101</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45909</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45909</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>44911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45742</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>44908</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45162</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45104</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45918</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45173</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45922</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45922</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45261</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45923</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46140</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45411</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45411</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44656</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>44881</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45244</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>44762</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45926</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45926</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>44514</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45203</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45933</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45933</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>46146</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45237</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45677</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45087</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45578</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45934</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45934</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45934</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45934</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45415</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>45710</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45344</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44678</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45937</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45258</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45939</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45474</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45938</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45938</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45939</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45086</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45939</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45939</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44944</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45898</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45008</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45153</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45947</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45605</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45237</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45006</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45951</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45951</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44971</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45954</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44781</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45954</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45626</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45626</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45666</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45236</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45236</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45194</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45140</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45140</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>46150</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45959</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45607</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45960</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45960</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>44809</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45960</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45281</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45189</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45097</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30297,7 +30297,7 @@
         <v>45273</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>44638</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45966</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45686</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45968</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45395</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45163</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45560</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>45974</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45975</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45974</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>45698</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31251,7 +31251,7 @@
         <v>45533</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45223</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45140</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31470,7 +31470,7 @@
         <v>45985</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45603</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45626</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45961</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45161</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45988</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>45992</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45992</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44626</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44914</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45398</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>44515</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>45071</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45427</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45994</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45994</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45994</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45166</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>45994</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>45994</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>44830</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45691</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45994</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45996</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45999</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44965</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46001</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>46001</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45356</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45601</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45280</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45498</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45197</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45316</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>46009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45357</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45009</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>46168</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>45163</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>44530</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45691</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45691</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45698</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45715</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45726</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45688</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45699</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45407</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45701</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45471</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>45603</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45603</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45043</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44847</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44812</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>44971</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45601</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>46029</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>44685</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45538</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45093</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46030</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45320</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>46030</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46125</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>44771</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>44817</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46041</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45070</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45671</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45771</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45002</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45484</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45225</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>46049</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45625</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>46048</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45140</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45120</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46055</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45166</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45166</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45166</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>44466</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>44959</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>44959</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>46177</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46062</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>44882</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46182</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>46182</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45072</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>44845</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45338</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>46071</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46181</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>46071</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45395</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>46077</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>45676</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45385</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>46063</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46063</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45626</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45626</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45626</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>46063</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45299</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45320</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45224</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45363</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>45166</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45225</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44501</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45384</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45163</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45597</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45565</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46087</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45225</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45225</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46091</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46190</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45250</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45775</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45104</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45008</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>46191</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>44763</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45328</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46101</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45086</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45552</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>45552</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45139</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45408</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>46112</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>44735</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>46114</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>46118</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>46121</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45461</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45573</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>46125</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>46128</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>45033</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>46128</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>45161</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>46245</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>45377</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45377</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45377</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>44858</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45363</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>45474</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45590</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>45573</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45227</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>45187</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>45947</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45558</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45257</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45691</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>45408</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>46248</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>45332</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45134</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>44593</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45242</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>44810</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45427</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45246</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45098</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45272</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46206</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>46255</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>46255</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45086</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>44565</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45604</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45070</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>46255</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>44642</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46255</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>46211</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>45273</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>46216</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>46216</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46247</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46216</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45059</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45059</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45168</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45168</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45038</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46211</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44909</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45750</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45745</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46261</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>46261</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45225</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46923,7 +46923,7 @@
         <v>44967</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44967</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>46261</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47142,7 +47142,7 @@
         <v>45643</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45041</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44497</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45090</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>44672</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45209</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>44613</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47658,7 +47658,7 @@
         <v>46262</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45544</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45158</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>46223</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45428</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45070</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45471</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>46267</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48242,7 +48242,7 @@
         <v>44658</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48315,7 +48315,7 @@
         <v>46223</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44488</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>46224</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48539,7 +48539,7 @@
         <v>46224</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48612,7 +48612,7 @@
         <v>46223</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>46224</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45015</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>45071</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>46227</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>46272</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>46272</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45231</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         <v>45782</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>46272</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>46271</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>46271</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>45934</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45785</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45785</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46135</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>46231</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>46232</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>45412</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>46274</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>45784</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46277</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>46277</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50374,7 +50374,7 @@
         <v>46277</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50447,7 +50447,7 @@
         <v>45709</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45157</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>45791</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>45790</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46238</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50812,7 +50812,7 @@
         <v>45797</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50885,7 +50885,7 @@
         <v>45799</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>46240</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51031,7 +51031,7 @@
         <v>45806</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51104,7 +51104,7 @@
         <v>45806</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51177,7 +51177,7 @@
         <v>45806</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51250,7 +51250,7 @@
         <v>45806</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45806</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45806</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45132</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45473</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45212</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51688,7 +51688,7 @@
         <v>45824</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>45727</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45727</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51907,7 +51907,7 @@
         <v>45826</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45730</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52053,7 +52053,7 @@
         <v>45743</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52126,7 +52126,7 @@
         <v>45720</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52199,7 +52199,7 @@
         <v>45833</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52272,7 +52272,7 @@
         <v>45835</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45835</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>45833</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52491,7 +52491,7 @@
         <v>45835</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>45835</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         <v>45835</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>45838</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52788,7 +52788,7 @@
         <v>45838</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52861,7 +52861,7 @@
         <v>45838</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52939,7 +52939,7 @@
         <v>45838</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45838</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45838</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>45838</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>45841</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45841</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45846</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45784</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45663</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45691</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45600</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45856</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>45862</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>45866</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45866</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>45868</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45880</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54195,7 +54195,7 @@
         <v>45400</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54268,7 +54268,7 @@
         <v>44658</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54341,7 +54341,7 @@
         <v>44854</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54414,7 +54414,7 @@
         <v>44771</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>44470</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>45169</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54633,7 +54633,7 @@
         <v>44747</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>44960</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54779,7 +54779,7 @@
         <v>44503</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45714</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>45171</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54998,7 +54998,7 @@
         <v>46066</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46083</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>46097</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45357</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46073</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45806</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>46097</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45264</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>46109</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>45603</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44553</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>44971</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45385</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45086</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>46001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45299</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45351</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45876</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>45264</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45236</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45603</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45134</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>46217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46223</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>45675</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44512</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44768</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45621</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45231</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45779</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>44498</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45351</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44861</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>44474</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>44679</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44512</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44533</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44817</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>44636</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44655</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>44868</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44823</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>44533</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44882</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44506</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44732</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44657</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44543</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44655</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>44852</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>44733</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44509</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44524</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44606</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44466</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>44480</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44638</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>44624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45626</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45626</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45471</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>45362</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45552</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45344</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45215</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>44881</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45075</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45407</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45085</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44771</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45357</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45698</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44817</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45398</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45250</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45428</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45474</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45443</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44809</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45242</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45086</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44512</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45467</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45320</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45715</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45699</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45688</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45691</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45726</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45043</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>44894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45334</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>46029</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>46030</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45484</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45484</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45797</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44914</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45162</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45273</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45341</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45605</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45795</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45889</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44873</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45889</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45643</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44656</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>46041</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45498</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45895</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45626</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46048</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45901</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45636</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45799</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45771</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46049</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45097</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45905</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44909</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45362</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45354</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45909</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45909</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>46055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45553</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45553</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45742</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44638</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45343</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44626</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>46062</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45348</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>44881</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44971</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44501</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>44672</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45806</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45806</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45926</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46071</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>46071</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45806</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45806</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>46077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45926</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>46063</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>46063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>46063</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45806</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45806</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45473</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45573</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>45385</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45933</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>46087</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>45934</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45934</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45132</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45934</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45324</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45324</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45343</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45934</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45547</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45547</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45547</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45937</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44945</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45938</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>44663</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>44724</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45244</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45225</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45939</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45070</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>46101</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44959</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45947</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45951</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45427</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45553</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45070</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>44911</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45411</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44831</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44908</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>46114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45225</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45225</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45959</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>46118</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45960</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45299</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45960</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44965</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45314</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46121</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44971</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>46125</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45611</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45966</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45966</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45968</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45602</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45974</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45974</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45411</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45411</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45474</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44503</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>46128</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45975</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45006</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46128</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45140</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45664</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45666</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45924</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45035</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45573</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45988</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45158</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45992</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45558</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45992</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45606</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45994</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45994</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45994</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45994</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45996</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45999</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46001</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45212</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44477</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44812</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45225</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45691</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45691</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45947</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44565</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>46001</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>46140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45161</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45043</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44810</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45224</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45231</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>46009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45299</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45701</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45691</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45835</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45824</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45237</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45070</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45992</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46101</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45223</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45686</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45140</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45008</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45134</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45743</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45730</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45727</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45180</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45727</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>46146</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44530</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45033</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45538</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45601</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45090</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44882</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>44917</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>46150</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45086</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45833</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44858</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45833</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45838</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45093</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45395</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45835</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45835</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45835</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45838</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45835</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45239</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45838</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45835</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45104</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45838</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45838</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45590</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45838</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45071</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44959</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45841</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45846</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45112</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45075</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45663</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45784</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45015</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45663</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>45691</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46168</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45856</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45600</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44477</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>44697</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44944</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44578</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>46125</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45168</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         <v>45168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45862</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>45161</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45771</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45162</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45750</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45363</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45162</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45866</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45866</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44947</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45868</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44959</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>44971</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>46177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45157</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45338</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45134</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45180</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>45086</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>46181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45643</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45227</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>46182</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45399</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>45187</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45043</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45324</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45162</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45163</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>46191</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45162</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46190</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45659</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45585</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45621</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45607</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45880</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45059</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>45059</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44663</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45377</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45377</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45377</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45471</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45558</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44558</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45191</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45328</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>44607</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>44607</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45281</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44763</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45412</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45316</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45225</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45181</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45159</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45344</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45173</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45166</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45201</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45194</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45194</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45166</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45166</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45166</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44638</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44638</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45231</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>45691</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45199</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45187</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>45560</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45427</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45098</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46206</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45427</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45666</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45676</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46253</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45166</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45710</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45140</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>45140</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45140</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>44845</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44658</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45626</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45626</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45626</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45233</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46211</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46211</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46255</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46255</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45681</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45363</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>46216</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>46216</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>46216</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45236</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45236</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>46261</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45197</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45244</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>45211</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41645,7 +41645,7 @@
         <v>46261</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>45685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44685</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>46261</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46262</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45162</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46223</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45282</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45189</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>46223</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>46223</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45239</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45247</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45461</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45190</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45227</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>46224</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>46224</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>46224</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>46267</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>44847</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>46272</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46227</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>46268</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45934</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44593</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44772</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45257</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45237</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>46272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>46271</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46271</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>46272</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>46231</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>45038</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>46274</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45087</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45745</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45245</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>46135</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45281</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45281</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45281</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>46232</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46277</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>46277</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45257</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>46238</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44515</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45258</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>44488</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46277</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>45606</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>44830</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>44606</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>46240</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>44566</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45008</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45384</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>44762</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>46245</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>44678</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45939</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46410,7 +46410,7 @@
         <v>44497</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45607</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45395</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>46247</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45139</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44896</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45071</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45009</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46057</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45361</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45598</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46248</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44760</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>44967</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>44967</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45625</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>44514</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45601</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45071</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>44945</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45104</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45320</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45565</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>44517</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45196</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>44613</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45120</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44636</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45533</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45258</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45246</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45163</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45597</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45272</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45089</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>44971</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45153</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45162</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45002</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45376</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45415</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>44894</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45482</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45518</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45544</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45582</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45683</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45775</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45006</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45321</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45002</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45227</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45227</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45124</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45140</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45608</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>44970</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45363</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>44636</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45224</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45412</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45265</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45265</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45320</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45209</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>44800</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45181</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45356</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>44466</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45163</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>44929</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45671</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45273</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45261</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45280</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45735</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45408</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45070</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45677</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45379</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45357</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45259</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45578</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45629</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45603</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45408</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>45332</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52922,7 +52922,7 @@
         <v>45072</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>45604</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45231</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45782</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45784</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45412</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>45785</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45785</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45709</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45790</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45157</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>45791</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>44658</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45400</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>44854</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>44771</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>44470</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54163,7 +54163,7 @@
         <v>45169</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>44747</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44960</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>44503</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45714</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>45171</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>46066</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>46083</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>46097</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>44690</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45357</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>46055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46073</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>45806</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45806</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>46097</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>45264</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>46109</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>45603</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>44553</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>44971</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45385</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45086</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>46001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45299</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45351</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>45876</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>45264</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45236</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45603</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>45134</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>46217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>46223</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>45675</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44512</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>44768</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45621</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>45231</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45779</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>44498</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>45351</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44861</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>44474</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>44679</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44518</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44512</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>44533</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44817</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>44636</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44655</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>44868</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44809</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>44823</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>44533</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44713</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44882</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44506</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44732</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44657</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>44543</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44655</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>44852</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>44733</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44509</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>44663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44524</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44606</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>44466</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44593</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>44480</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44638</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>44624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>44609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45626</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45626</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>44781</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45471</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>45246</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>45362</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45552</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45344</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45215</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>44881</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45075</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45407</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>45085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45085</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44771</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45357</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45698</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44817</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45398</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45250</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45428</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45474</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45443</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44809</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45242</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45086</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44512</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>45467</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45281</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45320</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45258</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45715</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45699</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45593</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45688</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45691</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45726</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45043</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>44894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45334</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>46029</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>46030</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>45484</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45484</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45797</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44914</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45162</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45273</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45341</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45605</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45795</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45889</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45889</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44873</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45889</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45643</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>44656</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>46041</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45498</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45895</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45626</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>46048</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45901</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45636</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45799</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45771</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46049</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45097</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45905</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>44909</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45362</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45354</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45909</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45909</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>46055</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45553</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45553</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45742</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44638</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45343</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44626</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>46062</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45348</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45918</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>44881</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44971</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44501</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>44672</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>45922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45923</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45806</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45806</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45926</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>46071</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>46071</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45806</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         <v>45806</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>46077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>45926</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>46063</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>46063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>46063</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45806</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45806</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>45473</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45573</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>45385</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>45933</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>46087</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>45934</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45934</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45132</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45934</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45324</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45324</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46091</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45343</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>45934</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45547</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45547</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45547</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45937</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44945</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45938</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>44663</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>44724</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45244</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45898</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45225</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45939</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45070</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>46101</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44959</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44959</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44959</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45947</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45951</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45427</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45553</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45070</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>44911</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45411</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44831</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>46112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44908</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>46114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45225</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45225</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45959</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>46118</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45960</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45299</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45960</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44965</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45314</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46121</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44971</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>46125</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45611</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45966</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45966</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>45968</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45602</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45974</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45974</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>45411</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45411</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45474</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>44503</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>46128</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45975</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45006</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46128</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45140</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45664</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45666</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45924</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45035</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45573</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45988</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45158</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>45992</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45558</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45992</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45606</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45994</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45994</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45994</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45994</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45996</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45999</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46001</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45212</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44477</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44812</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45225</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>45691</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>45691</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45947</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44565</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>46001</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>46140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45161</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45043</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44810</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45224</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45163</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45231</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>46009</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45299</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45701</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45691</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>45835</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45824</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45237</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45070</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45992</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>46101</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45223</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45686</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45140</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45008</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45134</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45743</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45730</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45727</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45180</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45727</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>46146</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44530</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45033</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45538</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45601</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45090</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>44882</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>44917</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>46150</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45086</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45833</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44858</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45833</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45838</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45093</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45395</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45835</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45835</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45835</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45838</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>45835</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45961</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45239</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45838</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45835</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31292,7 +31292,7 @@
         <v>45104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45104</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45838</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45838</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45203</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45590</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45838</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45071</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44959</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>45841</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45846</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45112</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45075</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45663</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45784</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45015</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45663</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>45691</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46168</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45856</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45600</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>44477</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>44697</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>44944</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>44578</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>46125</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45168</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
         <v>45168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45862</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>45161</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45771</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>45162</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45750</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45363</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45162</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45866</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45866</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>44947</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45868</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44959</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>44971</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>46177</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34524,7 +34524,7 @@
         <v>45157</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>45338</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45134</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34743,7 +34743,7 @@
         <v>45180</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34816,7 +34816,7 @@
         <v>45086</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>46181</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45643</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45227</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>46182</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45399</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>45187</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45043</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45324</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45162</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45163</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>46191</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45162</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46190</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45659</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45585</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45621</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45607</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45880</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45059</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>45059</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44663</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45377</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45377</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45377</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45471</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45558</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44558</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45191</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45328</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>44607</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>44607</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45281</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>44763</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45412</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45603</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45316</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45225</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45181</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45159</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>45344</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45173</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>45166</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45201</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45194</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45194</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>45166</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45166</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>44642</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>45166</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>44638</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44638</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45231</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38793,7 +38793,7 @@
         <v>45691</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>45199</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45187</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39012,7 +39012,7 @@
         <v>45560</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45427</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45098</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46206</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45427</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45666</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
         <v>45676</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>46253</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39596,7 +39596,7 @@
         <v>45166</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45710</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45140</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>45140</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45140</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>44845</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44658</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>45626</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45626</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45626</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>46255</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40399,7 +40399,7 @@
         <v>45233</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>46211</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46211</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>46255</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46255</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>46255</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45681</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45363</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>46216</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41056,7 +41056,7 @@
         <v>46216</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>46216</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45236</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45236</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>46261</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45197</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45244</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>45211</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41645,7 +41645,7 @@
         <v>46261</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>45685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44685</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>46261</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46262</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45162</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46223</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44824</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45282</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45189</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>46223</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>46223</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45239</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45247</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45461</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45190</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45227</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>46224</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>46224</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>46224</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>46267</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>44847</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>46272</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46227</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>46268</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45934</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44593</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44772</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45257</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45237</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>46272</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>46271</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46271</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45357</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44147,7 +44147,7 @@
         <v>46272</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>46231</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44293,7 +44293,7 @@
         <v>45038</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>46274</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45087</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45745</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45245</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>46135</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45281</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45281</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>45281</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>46232</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46277</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>46277</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45257</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>46238</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44515</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45388,7 +45388,7 @@
         <v>45258</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>44488</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>46277</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>45606</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>44830</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45753,7 +45753,7 @@
         <v>44606</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>46240</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45899,7 +45899,7 @@
         <v>44566</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45972,7 +45972,7 @@
         <v>45008</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>45384</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>44762</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>46245</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>44678</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         <v>45939</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46410,7 +46410,7 @@
         <v>44497</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45607</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45395</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>46247</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46702,7 +46702,7 @@
         <v>45139</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46775,7 +46775,7 @@
         <v>44896</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>45071</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45009</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46057</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45361</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47213,7 +47213,7 @@
         <v>45598</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>46248</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44760</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
         <v>44967</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>44967</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45625</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>44514</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45601</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45071</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>44945</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45104</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45320</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45565</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>44517</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45196</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>44613</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48386,7 +48386,7 @@
         <v>45120</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48459,7 +48459,7 @@
         <v>45237</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44636</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45533</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45258</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>45246</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>45163</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45597</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48970,7 +48970,7 @@
         <v>45272</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>45089</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>44971</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         <v>45153</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45162</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45002</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45376</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45415</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>44894</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45482</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45518</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>45544</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45582</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45683</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45775</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45006</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45321</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45002</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45227</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45227</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>45124</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45140</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45608</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>44970</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45363</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>44636</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45224</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45412</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45265</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45265</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45320</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45209</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>44800</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45181</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>45356</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>44466</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45163</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>44929</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45671</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45273</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45261</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45280</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>45735</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45408</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45070</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45677</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45379</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45357</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45259</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>45578</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45629</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45603</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45408</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52849,7 +52849,7 @@
         <v>45332</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52922,7 +52922,7 @@
         <v>45072</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>45604</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45231</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53141,7 +53141,7 @@
         <v>45782</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53214,7 +53214,7 @@
         <v>45784</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
         <v>45412</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>45785</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45785</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45709</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45790</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45157</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>45791</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>44658</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45400</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>44854</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54017,7 +54017,7 @@
         <v>44771</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>44470</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54163,7 +54163,7 @@
         <v>45169</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>44747</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>44960</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>44503</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45714</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>45171</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54601,7 +54601,7 @@
         <v>46066</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>46083</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>46097</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45357</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45603</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45675</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45264</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45134</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45385</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>45895</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45806</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>46055</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44512</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>46073</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45299</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46109</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>45621</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44553</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>46001</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44768</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45876</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45236</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46217</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46223</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44971</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>46294</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45231</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45779</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44498</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44861</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44512</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>44679</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>44474</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>44512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44533</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44636</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44655</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44868</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44858</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44809</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44533</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44713</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44497</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>44565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44552</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44491</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44506</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44732</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44657</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44543</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44655</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>44852</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44733</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44509</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44524</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44480</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44638</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44624</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44880</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44945</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45412</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45348</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44760</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44959</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44772</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45553</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44881</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44512</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45681</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45585</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44831</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45162</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45162</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45357</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44724</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45344</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44959</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45211</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45602</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45314</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45124</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>44894</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44578</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45006</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45237</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45709</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45070</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45201</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44894</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45558</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45321</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45157</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45376</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45247</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45791</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>46009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45357</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45606</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44959</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45159</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45363</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45691</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45265</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45265</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45691</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45691</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45698</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45715</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44887</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45688</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45699</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45701</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45603</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45603</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45043</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45889</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45889</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45889</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45795</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45889</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>44916</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45227</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46029</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45896</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45896</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>46030</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45636</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>46030</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45162</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45901</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45771</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45239</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45071</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45362</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45411</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45140</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45482</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45905</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46041</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45909</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45909</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45742</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45797</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45518</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44929</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44824</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46049</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45399</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45603</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45666</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>46048</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>46048</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45918</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45621</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45180</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44517</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45806</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45806</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45922</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45922</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45806</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45806</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45806</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45806</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44971</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45467</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45926</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45683</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45926</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45443</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44970</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45281</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45933</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45933</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>46062</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>44896</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45934</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45934</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45934</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45934</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45246</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45938</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>46071</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45299</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>46071</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45132</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45157</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45043</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45324</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45473</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44947</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>46077</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44636</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>44873</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45947</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45951</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>44917</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45606</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46063</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46063</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45951</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>46063</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45227</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45227</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45954</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45954</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45412</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45259</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45608</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44663</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>45231</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45663</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44800</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45960</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45960</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46087</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>46091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>44663</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45075</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45966</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45966</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44606</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45968</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44607</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44607</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44558</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45002</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45974</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45975</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>46101</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45212</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45974</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45974</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45194</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45257</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45281</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45281</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45281</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>46112</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45553</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45553</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45239</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45343</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45659</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46114</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45341</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46118</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45361</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45988</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45824</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45735</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45992</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46121</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45992</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45112</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45593</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45994</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45994</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45994</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45994</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45582</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45994</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46125</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45427</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45324</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45324</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45727</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45727</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44477</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45730</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>46128</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45996</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>46128</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45999</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45720</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>46001</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>46001</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44638</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>44638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45252</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45354</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45835</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45835</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45833</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45233</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45085</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45484</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>45835</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45343</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45835</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45089</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45835</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44636</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45838</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45187</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45244</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45611</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45838</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>45838</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45362</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>45838</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45838</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45043</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45245</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45838</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45841</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45947</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45558</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45547</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45547</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45547</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45075</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>44945</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45035</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45841</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45091</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45320</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45134</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45846</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45784</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44911</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44908</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>45162</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>45992</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45797</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>45104</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45895</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45629</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45173</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45663</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45691</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45261</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45835</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45600</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45411</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45411</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>44656</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>44881</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45244</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>44762</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45924</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45856</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45826</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45231</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45104</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44514</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45203</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45677</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45087</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45258</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46101</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45862</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45578</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45415</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45710</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45344</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>44678</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45866</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45258</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45866</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45474</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45086</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44944</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45868</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>45008</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>46140</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>45605</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45237</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>46146</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>44971</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44781</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45626</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45626</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45666</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45236</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45236</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45194</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45140</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45140</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45140</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45607</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>46150</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44809</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37208,7 +37208,7 @@
         <v>45281</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45189</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45097</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>45273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>44638</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45686</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45961</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45395</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45163</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45560</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45698</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45533</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45223</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45140</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45603</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45626</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46168</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45880</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>46125</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45771</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44626</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44914</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>46177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45398</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46182</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>44971</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>44515</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45199</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45071</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45427</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>46181</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45166</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>44830</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45691</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44965</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>46190</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45356</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45601</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>46191</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45280</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45498</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45197</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45316</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45357</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45009</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45163</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44530</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45407</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45471</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>44847</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>44812</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>44971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45601</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44685</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45538</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45093</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>45320</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44771</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45215</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>44817</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>46206</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45671</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45484</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>46211</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45225</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46216</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>46216</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>46216</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45625</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>46211</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45140</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45120</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>46261</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>46261</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>46261</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45166</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45166</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45166</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>46262</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>44959</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>44959</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>46223</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46267</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>46223</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44882</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45072</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>46224</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>46224</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>46223</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>46224</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>44845</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45338</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46268</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>46227</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46272</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45395</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>46272</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>46272</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>45676</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44777,7 +44777,7 @@
         <v>45385</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46271</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44923,7 +44923,7 @@
         <v>46271</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>45626</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45626</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45626</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45934</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45299</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45181</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45320</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>45224</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>46135</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>46231</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>46232</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>46274</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46277</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>46277</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>45363</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45166</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>45225</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45190</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>46238</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44501</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45384</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45163</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45597</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>45565</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45225</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45250</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45775</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45104</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>44763</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45328</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>46240</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>45939</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45086</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>46277</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45552</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45552</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45139</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45408</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>44735</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>46245</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45379</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>45461</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45573</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>45598</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>46248</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45033</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45161</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>46057</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>46293</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45377</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45377</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45377</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>46293</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>46293</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>46247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>44858</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45363</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>45474</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45590</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45573</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45227</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45187</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45257</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45939</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45691</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>46255</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45408</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>46297</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>46255</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45332</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45134</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>46255</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>46255</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>46297</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>46253</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50690,7 +50690,7 @@
         <v>46297</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>44593</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45242</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>44810</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45427</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>45246</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45098</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>45272</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45086</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>44565</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45604</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45070</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>44642</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45273</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45059</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45059</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>45168</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45168</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45038</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>44909</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>45750</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45745</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45225</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52369,7 +52369,7 @@
         <v>44967</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>44967</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45643</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>45041</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>44497</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45090</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>44672</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45209</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>44613</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>45544</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>45158</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45428</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45070</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>45471</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>44658</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>44488</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45015</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45071</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45231</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45782</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45785</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>45785</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45412</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45784</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45400</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>44658</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>44854</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>44771</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45169</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>44747</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54564,7 +54564,7 @@
         <v>44960</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54637,7 +54637,7 @@
         <v>44503</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>45714</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54783,7 +54783,7 @@
         <v>45171</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54856,7 +54856,7 @@
         <v>46066</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>44690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>46083</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>46097</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45357</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>46097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45785</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>45603</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45675</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>45264</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45134</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>45351</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45385</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>45895</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45086</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>45806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3432,7 +3432,7 @@
         <v>45806</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>46055</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44512</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>46073</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>45299</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>46109</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>45621</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44553</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>46001</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44768</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45876</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45236</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46217</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45568</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46223</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>44971</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>46294</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>45231</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>45779</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44498</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>45351</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44861</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44512</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>44679</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>44474</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>44512</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44533</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>44531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44726</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44636</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44655</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44868</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44858</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44809</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44533</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44713</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44497</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>44565</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44552</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44491</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44506</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44732</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44657</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44543</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44854</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44776</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44655</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44775</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>44852</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44733</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44532</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44750</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44509</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44621</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44606</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44524</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>44593</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44593</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>44480</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44638</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>44624</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>44880</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44945</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45412</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45348</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44760</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44959</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44772</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>45553</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44477</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>45180</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44881</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44512</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45681</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45585</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44831</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45162</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>45162</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45357</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44724</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45344</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44959</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45211</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45602</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45314</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45124</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>44894</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44578</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44895</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45006</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45237</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45709</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45070</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45201</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44894</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45558</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45321</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45157</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45376</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45247</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45791</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>46009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45357</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45606</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44959</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45159</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45363</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45691</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45265</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45265</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45691</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45691</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45698</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45715</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>44887</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45688</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45699</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45701</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45603</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45603</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45043</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45889</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45889</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45889</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45795</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45889</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45895</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>44916</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>45895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45227</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46029</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45896</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45896</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>46030</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45636</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>46030</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45162</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45901</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45771</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45239</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45071</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45362</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45162</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45411</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45140</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45482</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45905</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46041</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45909</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45909</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45742</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45797</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45518</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44566</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>44929</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44824</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46049</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45799</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45399</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45603</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45666</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>46048</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>46048</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45918</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45621</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45180</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44517</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45806</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45806</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45922</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45922</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45806</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45806</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45806</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45806</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44971</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45467</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45926</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45683</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45926</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45443</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44970</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>45281</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45933</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45933</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>46062</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>44896</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45934</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45934</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45934</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45934</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45246</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45938</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45938</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>46071</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45299</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>46071</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45132</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45157</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45043</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45324</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45473</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44947</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>46077</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44636</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>44873</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45947</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45951</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>44917</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45606</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46063</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46063</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45951</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>46063</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45227</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45227</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45954</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45954</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45412</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45259</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45608</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44663</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>45231</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45663</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>44800</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45960</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45960</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>46087</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>46091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>44503</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>44663</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45075</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45966</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>45966</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44606</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>45968</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44607</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44607</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44558</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45002</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>45974</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45975</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>45282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>46101</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45212</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45974</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45974</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45194</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45257</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45281</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45281</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45281</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>46112</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45553</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45553</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45239</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45343</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45659</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>46114</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45341</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>46118</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45361</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45988</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45824</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45735</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45992</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46121</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45992</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45112</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45593</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45994</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45994</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45994</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45994</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45994</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45582</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45994</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>46125</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45427</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45324</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45324</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45727</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45727</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44477</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45826</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45730</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45743</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>46128</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45996</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>46128</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45999</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45720</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>46001</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>46001</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44638</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>44638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45252</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45354</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45833</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45835</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45835</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45833</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45233</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45085</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45484</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>45835</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45343</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45835</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45089</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45835</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44636</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45838</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45187</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45244</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30515,7 +30515,7 @@
         <v>45611</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45838</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>45838</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>45362</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>45838</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45838</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45043</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45245</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45838</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45841</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45947</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45558</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45547</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45547</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45547</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45075</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>44945</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45035</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45841</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45091</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45320</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45134</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45846</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45784</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44911</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32453,7 +32453,7 @@
         <v>44908</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32526,7 +32526,7 @@
         <v>45162</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32599,7 +32599,7 @@
         <v>45992</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45797</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>45104</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45895</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45629</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>45173</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45663</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45691</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45261</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
         <v>45835</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45600</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45411</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>45411</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>44656</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>44881</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45244</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>44762</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45924</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45856</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45826</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45231</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45104</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>44514</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45203</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45677</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45087</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45258</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46101</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45862</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45578</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45415</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45710</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45344</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>44678</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45866</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45258</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45866</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45474</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45086</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44944</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>45868</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>45008</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35743,7 +35743,7 @@
         <v>45153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>46140</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>45605</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45237</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>46146</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>44971</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>44781</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45626</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45626</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45666</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45236</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>45236</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36697,7 +36697,7 @@
         <v>45194</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45140</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45140</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45140</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45607</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>46150</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>44809</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37208,7 +37208,7 @@
         <v>45281</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45189</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45097</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>45273</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>44638</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45686</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>45961</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45395</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37797,7 +37797,7 @@
         <v>45163</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45560</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45698</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45533</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45223</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45140</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45603</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45626</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46168</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45880</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>46125</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45771</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>44626</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44914</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>46177</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45398</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>46182</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46182</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>44971</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>44515</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45199</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45071</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45427</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>46181</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45166</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>44830</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>45691</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44965</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>46190</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45356</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45601</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40148,7 +40148,7 @@
         <v>46191</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40221,7 +40221,7 @@
         <v>45280</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45498</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45197</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45316</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>45357</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45009</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45163</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>44530</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40820,7 +40820,7 @@
         <v>45407</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45471</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>44847</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>44812</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>44971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45601</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44685</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45538</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45093</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>45320</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44771</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45215</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>44817</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>46206</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45671</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45484</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>46211</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45225</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46216</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>46216</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>46216</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>45625</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>46211</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45140</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45120</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>46261</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>46261</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>46261</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45166</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45166</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45166</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>46262</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>44959</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>44959</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>46223</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46267</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>46223</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44882</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45072</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>46224</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>46224</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>46223</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>46224</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>44845</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45338</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46268</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>46227</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46272</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45395</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>46272</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>46272</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44704,7 +44704,7 @@
         <v>45676</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44777,7 +44777,7 @@
         <v>45385</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46271</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44923,7 +44923,7 @@
         <v>46271</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>45626</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45626</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45626</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>45934</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45299</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         <v>45181</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45320</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>45224</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45580,7 +45580,7 @@
         <v>46135</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45653,7 +45653,7 @@
         <v>46231</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>46232</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>46274</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46277</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>46277</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>45363</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45166</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>45225</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45190</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>46238</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44501</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45384</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>45163</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>45597</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>45565</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45225</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45250</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45775</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45104</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45008</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>44763</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45328</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>46240</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>45939</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45086</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>46277</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45552</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45552</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45139</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45408</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>44735</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>46245</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45379</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>45461</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45573</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>45598</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48354,7 +48354,7 @@
         <v>46248</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>45033</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45161</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>46057</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>46293</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45377</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45377</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45377</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>46293</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>46293</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>46247</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>44858</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45363</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>45474</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45590</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>46294</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45573</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45227</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45187</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45257</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45939</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45691</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>46255</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45408</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>46297</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>46255</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45332</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45134</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>46255</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>46255</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>46297</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>46253</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50690,7 +50690,7 @@
         <v>46297</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>44593</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45242</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>44810</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45427</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>45246</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45098</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>45272</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45086</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>44565</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>45604</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45070</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>44642</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45273</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45059</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45059</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>45168</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45168</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45038</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>44909</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>45750</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45745</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52296,7 +52296,7 @@
         <v>45225</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52369,7 +52369,7 @@
         <v>44967</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>44967</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45643</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>45041</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>44497</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45090</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>44672</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45209</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>44613</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>45544</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53104,7 +53104,7 @@
         <v>45158</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45428</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45070</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>45471</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>44658</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>44488</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45015</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45071</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45231</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45782</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45785</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>45785</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45412</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54053,7 +54053,7 @@
         <v>45784</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45400</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>44658</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>44854</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>44771</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45169</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>44747</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54564,7 +54564,7 @@
         <v>44960</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54637,7 +54637,7 @@
         <v>44503</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54710,7 +54710,7 @@
         <v>45714</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54783,7 +54783,7 @@
         <v>45171</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54856,7 +54856,7 @@
         <v>46066</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -644,13 +644,13 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -660,6 +660,7 @@
 Drillsnäppa
 Järnsparv
 Mindre tåtelsmygare
+Hagfingersvamp
 Korallrot
 Mönjevaxing
 Trådticka
@@ -731,7 +732,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +840,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -947,7 +948,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1059,7 +1060,7 @@
         <v>44690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1172,7 @@
         <v>45357</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1283,7 +1284,7 @@
         <v>46083</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1396,7 @@
         <v>46097</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1507,7 +1508,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1620,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1726,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1836,7 @@
         <v>45785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1942,7 @@
         <v>46097</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2053,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2164,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2268,7 +2269,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2374,7 @@
         <v>45264</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2479,7 @@
         <v>45351</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2583,7 +2584,7 @@
         <v>45895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2689,7 @@
         <v>45231</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2797,7 +2798,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2902,7 +2903,7 @@
         <v>45806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3011,7 +3012,7 @@
         <v>45806</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3120,7 +3121,7 @@
         <v>45236</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3225,7 +3226,7 @@
         <v>45264</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3331,7 @@
         <v>45603</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3440,7 +3441,7 @@
         <v>45134</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3545,7 +3546,7 @@
         <v>45603</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3650,7 +3651,7 @@
         <v>44971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3755,7 +3756,7 @@
         <v>45385</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3860,7 +3861,7 @@
         <v>45086</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3965,7 +3966,7 @@
         <v>45876</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4071,7 @@
         <v>45299</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4175,7 +4176,7 @@
         <v>45675</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4280,7 +4281,7 @@
         <v>46109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4385,7 +4386,7 @@
         <v>44512</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4490,7 +4491,7 @@
         <v>44553</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4595,7 +4596,7 @@
         <v>46001</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4700,7 +4701,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4805,7 +4806,7 @@
         <v>44768</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4914,7 +4915,7 @@
         <v>45621</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5019,7 +5020,7 @@
         <v>46073</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5128,7 +5129,7 @@
         <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5238,7 +5239,7 @@
         <v>46217</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5343,7 +5344,7 @@
         <v>46223</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5454,7 @@
         <v>46294</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5562,7 +5563,7 @@
         <v>44498</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5667,7 +5668,7 @@
         <v>45351</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5773,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5846,7 @@
         <v>44861</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5919,7 @@
         <v>44679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5992,7 @@
         <v>44512</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6065,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6138,7 @@
         <v>44512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6215,7 +6216,7 @@
         <v>44533</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6288,7 +6289,7 @@
         <v>44531</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6361,7 +6362,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6434,7 +6435,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6507,7 +6508,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6580,7 +6581,7 @@
         <v>44817</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6653,7 +6654,7 @@
         <v>44636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6726,7 +6727,7 @@
         <v>44655</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6799,7 +6800,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6872,7 +6873,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6945,7 +6946,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7018,7 +7019,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7091,7 +7092,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7164,7 +7165,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7237,7 +7238,7 @@
         <v>44713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7310,7 +7311,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7383,7 +7384,7 @@
         <v>44565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7456,7 +7457,7 @@
         <v>44882</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7529,7 +7530,7 @@
         <v>44552</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7602,7 +7603,7 @@
         <v>44491</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7675,7 +7676,7 @@
         <v>44750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7748,7 +7749,7 @@
         <v>44506</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7821,7 +7822,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7894,7 +7895,7 @@
         <v>44621</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7967,7 +7968,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8040,7 +8041,7 @@
         <v>44606</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8113,7 +8114,7 @@
         <v>44732</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8186,7 +8187,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8259,7 +8260,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8337,7 +8338,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8410,7 +8411,7 @@
         <v>44854</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8483,7 +8484,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8556,7 +8557,7 @@
         <v>44775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8629,7 +8630,7 @@
         <v>44655</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8702,7 +8703,7 @@
         <v>44593</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8775,7 +8776,7 @@
         <v>44852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8848,7 +8849,7 @@
         <v>44882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8921,7 +8922,7 @@
         <v>44656</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8994,7 +8995,7 @@
         <v>44609</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9067,7 +9068,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9140,7 +9141,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9213,7 +9214,7 @@
         <v>44663</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9286,7 +9287,7 @@
         <v>44532</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9359,7 +9360,7 @@
         <v>44594</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9432,7 +9433,7 @@
         <v>44480</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9505,7 +9506,7 @@
         <v>44638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9578,7 +9579,7 @@
         <v>44624</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9651,7 +9652,7 @@
         <v>44609</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9724,7 +9725,7 @@
         <v>44881</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9797,7 +9798,7 @@
         <v>45075</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9870,7 +9871,7 @@
         <v>45407</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9943,7 +9944,7 @@
         <v>44880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10016,7 +10017,7 @@
         <v>45153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10089,7 +10090,7 @@
         <v>45090</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10162,7 +10163,7 @@
         <v>45162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10235,7 +10236,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10308,7 +10309,7 @@
         <v>45698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10381,7 +10382,7 @@
         <v>45002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10454,7 +10455,7 @@
         <v>44917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10532,7 +10533,7 @@
         <v>44771</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10605,7 +10606,7 @@
         <v>45626</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10678,7 +10679,7 @@
         <v>45626</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10751,7 +10752,7 @@
         <v>45085</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10824,7 +10825,7 @@
         <v>45085</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10897,7 +10898,7 @@
         <v>45376</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10970,7 +10971,7 @@
         <v>45357</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11048,7 +11049,7 @@
         <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11121,7 +11122,7 @@
         <v>45415</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11194,7 +11195,7 @@
         <v>44894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11267,7 +11268,7 @@
         <v>44817</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11340,7 +11341,7 @@
         <v>45086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11413,7 +11414,7 @@
         <v>45471</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11486,7 +11487,7 @@
         <v>45482</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11559,7 +11560,7 @@
         <v>44512</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11637,7 +11638,7 @@
         <v>45518</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11710,7 +11711,7 @@
         <v>45344</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11783,7 +11784,7 @@
         <v>45215</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11856,7 +11857,7 @@
         <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11929,7 +11930,7 @@
         <v>44858</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12002,7 +12003,7 @@
         <v>45544</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12075,7 +12076,7 @@
         <v>45398</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12148,7 +12149,7 @@
         <v>45250</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12221,7 +12222,7 @@
         <v>45428</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12294,7 +12295,7 @@
         <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12367,7 +12368,7 @@
         <v>45395</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12440,7 +12441,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12513,7 +12514,7 @@
         <v>45582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12586,7 +12587,7 @@
         <v>45239</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12659,7 +12660,7 @@
         <v>45683</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12732,7 +12733,7 @@
         <v>45246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12805,7 +12806,7 @@
         <v>45775</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12878,7 +12879,7 @@
         <v>45104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12951,7 +12952,7 @@
         <v>45104</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13024,7 +13025,7 @@
         <v>45006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13102,7 +13103,7 @@
         <v>45203</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13175,7 +13176,7 @@
         <v>45590</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13248,7 +13249,7 @@
         <v>45474</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13321,7 +13322,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13394,7 +13395,7 @@
         <v>44809</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13467,7 +13468,7 @@
         <v>45071</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13540,7 +13541,7 @@
         <v>45321</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13613,7 +13614,7 @@
         <v>44916</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13686,7 +13687,7 @@
         <v>44916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13759,7 +13760,7 @@
         <v>45002</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13832,7 +13833,7 @@
         <v>44959</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13905,7 +13906,7 @@
         <v>45227</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13978,7 +13979,7 @@
         <v>45227</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14051,7 +14052,7 @@
         <v>45124</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14124,7 +14125,7 @@
         <v>45140</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14197,7 +14198,7 @@
         <v>45608</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14270,7 +14271,7 @@
         <v>44970</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14343,7 +14344,7 @@
         <v>45363</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14416,7 +14417,7 @@
         <v>45242</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14489,7 +14490,7 @@
         <v>44636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14562,7 +14563,7 @@
         <v>45224</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14635,7 +14636,7 @@
         <v>45086</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14708,7 +14709,7 @@
         <v>45112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14781,7 +14782,7 @@
         <v>45075</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14854,7 +14855,7 @@
         <v>45663</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14927,7 +14928,7 @@
         <v>45362</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15005,7 +15006,7 @@
         <v>45552</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15078,7 +15079,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15151,7 +15152,7 @@
         <v>45412</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15224,7 +15225,7 @@
         <v>45265</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15297,7 +15298,7 @@
         <v>45265</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15370,7 +15371,7 @@
         <v>45320</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15443,7 +15444,7 @@
         <v>45209</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15516,7 +15517,7 @@
         <v>44800</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15589,7 +15590,7 @@
         <v>45181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15662,7 +15663,7 @@
         <v>45015</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15735,7 +15736,7 @@
         <v>45356</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15808,7 +15809,7 @@
         <v>45159</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15881,7 +15882,7 @@
         <v>45281</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15954,7 +15955,7 @@
         <v>45467</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16027,7 +16028,7 @@
         <v>45320</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16100,7 +16101,7 @@
         <v>45163</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16173,7 +16174,7 @@
         <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16246,7 +16247,7 @@
         <v>44887</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16324,7 +16325,7 @@
         <v>44894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16397,7 +16398,7 @@
         <v>45593</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16470,7 +16471,7 @@
         <v>45162</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16543,7 +16544,7 @@
         <v>44929</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16616,7 +16617,7 @@
         <v>45671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16689,7 +16690,7 @@
         <v>44697</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16762,7 +16763,7 @@
         <v>44944</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16835,7 +16836,7 @@
         <v>44578</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16908,7 +16909,7 @@
         <v>45168</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16981,7 +16982,7 @@
         <v>45168</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17054,7 +17055,7 @@
         <v>45273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17127,7 +17128,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17200,7 +17201,7 @@
         <v>45161</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17273,7 +17274,7 @@
         <v>45261</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17346,7 +17347,7 @@
         <v>45795</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17419,7 +17420,7 @@
         <v>45162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17492,7 +17493,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17565,7 +17566,7 @@
         <v>45735</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17638,7 +17639,7 @@
         <v>45484</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17711,7 +17712,7 @@
         <v>45750</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17784,7 +17785,7 @@
         <v>45484</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17857,7 +17858,7 @@
         <v>45889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17930,7 +17931,7 @@
         <v>45363</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18003,7 +18004,7 @@
         <v>45162</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18076,7 +18077,7 @@
         <v>45889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18149,7 +18150,7 @@
         <v>45408</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18222,7 +18223,7 @@
         <v>44895</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18295,7 +18296,7 @@
         <v>44947</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18368,7 +18369,7 @@
         <v>45070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18441,7 +18442,7 @@
         <v>44914</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18514,7 +18515,7 @@
         <v>44959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18587,7 +18588,7 @@
         <v>45889</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18660,7 +18661,7 @@
         <v>45889</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18733,7 +18734,7 @@
         <v>45643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18806,7 +18807,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18879,7 +18880,7 @@
         <v>45895</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18957,7 +18958,7 @@
         <v>45895</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19030,7 +19031,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19103,7 +19104,7 @@
         <v>45273</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19176,7 +19177,7 @@
         <v>45341</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19249,7 +19250,7 @@
         <v>45677</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19322,7 +19323,7 @@
         <v>45379</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19395,7 +19396,7 @@
         <v>45605</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19468,7 +19469,7 @@
         <v>45357</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19541,7 +19542,7 @@
         <v>45259</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19614,7 +19615,7 @@
         <v>45578</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19687,7 +19688,7 @@
         <v>45901</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19760,7 +19761,7 @@
         <v>45629</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19833,7 +19834,7 @@
         <v>45603</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19911,7 +19912,7 @@
         <v>45408</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19984,7 +19985,7 @@
         <v>45636</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20057,7 +20058,7 @@
         <v>44873</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20130,7 +20131,7 @@
         <v>45771</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20203,7 +20204,7 @@
         <v>44971</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20276,7 +20277,7 @@
         <v>45332</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20349,7 +20350,7 @@
         <v>45072</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20422,7 +20423,7 @@
         <v>45604</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20495,7 +20496,7 @@
         <v>44656</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20568,7 +20569,7 @@
         <v>45498</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20646,7 +20647,7 @@
         <v>45157</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20719,7 +20720,7 @@
         <v>45905</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20792,7 +20793,7 @@
         <v>45626</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20865,7 +20866,7 @@
         <v>45338</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20938,7 +20939,7 @@
         <v>45134</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21011,7 +21012,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21084,7 +21085,7 @@
         <v>45909</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21157,7 +21158,7 @@
         <v>45180</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21230,7 +21231,7 @@
         <v>45086</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21303,7 +21304,7 @@
         <v>45231</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21376,7 +21377,7 @@
         <v>45742</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21449,7 +21450,7 @@
         <v>45782</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21522,7 +21523,7 @@
         <v>45643</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21595,7 +21596,7 @@
         <v>45097</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21668,7 +21669,7 @@
         <v>45227</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21741,7 +21742,7 @@
         <v>44909</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21814,7 +21815,7 @@
         <v>45362</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21892,7 +21893,7 @@
         <v>45399</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21965,7 +21966,7 @@
         <v>45784</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22038,7 +22039,7 @@
         <v>45354</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22111,7 +22112,7 @@
         <v>45187</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22184,7 +22185,7 @@
         <v>45412</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22257,7 +22258,7 @@
         <v>45553</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22330,7 +22331,7 @@
         <v>45553</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22403,7 +22404,7 @@
         <v>45043</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22476,7 +22477,7 @@
         <v>45785</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22549,7 +22550,7 @@
         <v>44638</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22627,7 +22628,7 @@
         <v>45343</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22700,7 +22701,7 @@
         <v>45324</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22778,7 +22779,7 @@
         <v>45918</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22851,7 +22852,7 @@
         <v>44626</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22924,7 +22925,7 @@
         <v>45162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22997,7 +22998,7 @@
         <v>45348</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23070,7 +23071,7 @@
         <v>44881</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23143,7 +23144,7 @@
         <v>45163</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23216,7 +23217,7 @@
         <v>44971</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23289,7 +23290,7 @@
         <v>45709</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23362,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23435,7 +23436,7 @@
         <v>44672</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23508,7 +23509,7 @@
         <v>45922</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23581,7 +23582,7 @@
         <v>45922</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23654,7 +23655,7 @@
         <v>45162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23727,7 +23728,7 @@
         <v>45923</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23800,7 +23801,7 @@
         <v>45790</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23873,7 +23874,7 @@
         <v>45659</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23946,7 +23947,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24019,7 +24020,7 @@
         <v>45585</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24092,7 +24093,7 @@
         <v>45621</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24165,7 +24166,7 @@
         <v>45926</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24238,7 +24239,7 @@
         <v>45041</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24311,7 +24312,7 @@
         <v>45607</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24384,7 +24385,7 @@
         <v>45157</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24457,7 +24458,7 @@
         <v>45059</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24530,7 +24531,7 @@
         <v>45059</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24603,7 +24604,7 @@
         <v>45791</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24676,7 +24677,7 @@
         <v>44663</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24749,7 +24750,7 @@
         <v>45377</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24822,7 +24823,7 @@
         <v>45377</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24895,7 +24896,7 @@
         <v>45377</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24968,7 +24969,7 @@
         <v>45471</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25041,7 +25042,7 @@
         <v>45558</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25114,7 +25115,7 @@
         <v>45573</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25187,7 +25188,7 @@
         <v>45385</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25260,7 +25261,7 @@
         <v>44558</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25333,7 +25334,7 @@
         <v>45191</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25406,7 +25407,7 @@
         <v>45797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25479,7 +25480,7 @@
         <v>45328</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25552,7 +25553,7 @@
         <v>45324</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25625,7 +25626,7 @@
         <v>45324</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25703,7 +25704,7 @@
         <v>45343</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25776,7 +25777,7 @@
         <v>44607</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25849,7 +25850,7 @@
         <v>44607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25922,7 +25923,7 @@
         <v>45547</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26000,7 +26001,7 @@
         <v>45547</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26078,7 +26079,7 @@
         <v>45547</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26156,7 +26157,7 @@
         <v>45933</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26229,7 +26230,7 @@
         <v>44945</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26302,7 +26303,7 @@
         <v>45934</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26375,7 +26376,7 @@
         <v>45934</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26448,7 +26449,7 @@
         <v>45934</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26521,7 +26522,7 @@
         <v>45281</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26594,7 +26595,7 @@
         <v>44763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26667,7 +26668,7 @@
         <v>44663</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26740,7 +26741,7 @@
         <v>44724</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26813,7 +26814,7 @@
         <v>45412</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26886,7 +26887,7 @@
         <v>45244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26959,7 +26960,7 @@
         <v>45603</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27037,7 +27038,7 @@
         <v>45316</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27110,7 +27111,7 @@
         <v>45799</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27183,7 +27184,7 @@
         <v>45933</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27256,7 +27257,7 @@
         <v>45225</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27329,7 +27330,7 @@
         <v>45181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27402,7 +27403,7 @@
         <v>45934</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27475,7 +27476,7 @@
         <v>45344</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27548,7 +27549,7 @@
         <v>45173</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27621,7 +27622,7 @@
         <v>45166</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27694,7 +27695,7 @@
         <v>45937</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27767,7 +27768,7 @@
         <v>45225</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27840,7 +27841,7 @@
         <v>45806</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27913,7 +27914,7 @@
         <v>45806</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27986,7 +27987,7 @@
         <v>45070</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28059,7 +28060,7 @@
         <v>45201</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28132,7 +28133,7 @@
         <v>45938</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28205,7 +28206,7 @@
         <v>45938</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28278,7 +28279,7 @@
         <v>45194</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28351,7 +28352,7 @@
         <v>45194</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28424,7 +28425,7 @@
         <v>45806</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28497,7 +28498,7 @@
         <v>45166</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28570,7 +28571,7 @@
         <v>45166</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28643,7 +28644,7 @@
         <v>44642</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28716,7 +28717,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28789,7 +28790,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28862,7 +28863,7 @@
         <v>44959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28935,7 +28936,7 @@
         <v>45166</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29008,7 +29009,7 @@
         <v>44638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29086,7 +29087,7 @@
         <v>44638</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29164,7 +29165,7 @@
         <v>45473</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29237,7 +29238,7 @@
         <v>45231</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29315,7 +29316,7 @@
         <v>45691</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29388,7 +29389,7 @@
         <v>45132</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29461,7 +29462,7 @@
         <v>45199</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29534,7 +29535,7 @@
         <v>45427</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29607,7 +29608,7 @@
         <v>45187</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29680,7 +29681,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29753,7 +29754,7 @@
         <v>45560</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29826,7 +29827,7 @@
         <v>45553</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29899,7 +29900,7 @@
         <v>45427</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29972,7 +29973,7 @@
         <v>45939</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30045,7 +30046,7 @@
         <v>45098</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30118,7 +30119,7 @@
         <v>45427</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30191,7 +30192,7 @@
         <v>45666</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30264,7 +30265,7 @@
         <v>45676</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30337,7 +30338,7 @@
         <v>44735</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30410,7 +30411,7 @@
         <v>45070</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30483,7 +30484,7 @@
         <v>45166</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30556,7 +30557,7 @@
         <v>44911</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30629,7 +30630,7 @@
         <v>45411</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30702,7 +30703,7 @@
         <v>45710</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30775,7 +30776,7 @@
         <v>45140</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30848,7 +30849,7 @@
         <v>45140</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30921,7 +30922,7 @@
         <v>45140</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30994,7 +30995,7 @@
         <v>44845</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31067,7 +31068,7 @@
         <v>44658</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31140,7 +31141,7 @@
         <v>44831</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31213,7 +31214,7 @@
         <v>45626</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31286,7 +31287,7 @@
         <v>45626</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31359,7 +31360,7 @@
         <v>45626</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31432,7 +31433,7 @@
         <v>45212</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31505,7 +31506,7 @@
         <v>44908</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31578,7 +31579,7 @@
         <v>45225</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31651,7 +31652,7 @@
         <v>45225</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31724,7 +31725,7 @@
         <v>45299</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31797,7 +31798,7 @@
         <v>44965</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31870,7 +31871,7 @@
         <v>45233</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31943,7 +31944,7 @@
         <v>45314</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32016,7 +32017,7 @@
         <v>45947</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32089,7 +32090,7 @@
         <v>45824</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32162,7 +32163,7 @@
         <v>44971</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32235,7 +32236,7 @@
         <v>45681</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32308,7 +32309,7 @@
         <v>45611</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32381,7 +32382,7 @@
         <v>45951</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32454,7 +32455,7 @@
         <v>45363</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32527,7 +32528,7 @@
         <v>45826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32600,7 +32601,7 @@
         <v>45720</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32673,7 +32674,7 @@
         <v>45743</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32746,7 +32747,7 @@
         <v>45730</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32819,7 +32820,7 @@
         <v>45727</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32892,7 +32893,7 @@
         <v>45727</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32965,7 +32966,7 @@
         <v>45236</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33038,7 +33039,7 @@
         <v>45236</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33111,7 +33112,7 @@
         <v>45951</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33184,7 +33185,7 @@
         <v>45954</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33257,7 +33258,7 @@
         <v>45954</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33335,7 +33336,7 @@
         <v>45602</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33408,7 +33409,7 @@
         <v>45960</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33481,7 +33482,7 @@
         <v>45960</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33554,7 +33555,7 @@
         <v>45959</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33627,7 +33628,7 @@
         <v>45960</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33700,7 +33701,7 @@
         <v>45960</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33773,7 +33774,7 @@
         <v>45411</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33846,7 +33847,7 @@
         <v>45411</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33919,7 +33920,7 @@
         <v>45197</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33997,7 +33998,7 @@
         <v>45244</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34070,7 +34071,7 @@
         <v>45211</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34143,7 +34144,7 @@
         <v>45833</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34216,7 +34217,7 @@
         <v>45833</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34289,7 +34290,7 @@
         <v>45685</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34362,7 +34363,7 @@
         <v>45474</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34435,7 +34436,7 @@
         <v>45838</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34508,7 +34509,7 @@
         <v>45835</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34581,7 +34582,7 @@
         <v>45835</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34654,7 +34655,7 @@
         <v>45835</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34727,7 +34728,7 @@
         <v>45838</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34805,7 +34806,7 @@
         <v>44685</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34878,7 +34879,7 @@
         <v>44503</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34951,7 +34952,7 @@
         <v>45835</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35024,7 +35025,7 @@
         <v>45838</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35097,7 +35098,7 @@
         <v>45835</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35170,7 +35171,7 @@
         <v>45006</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35248,7 +35249,7 @@
         <v>45838</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35326,7 +35327,7 @@
         <v>45838</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35404,7 +35405,7 @@
         <v>45966</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35477,7 +35478,7 @@
         <v>45162</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35550,7 +35551,7 @@
         <v>45966</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35623,7 +35624,7 @@
         <v>45838</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35701,7 +35702,7 @@
         <v>45140</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35774,7 +35775,7 @@
         <v>45664</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35847,7 +35848,7 @@
         <v>45838</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35925,7 +35926,7 @@
         <v>44824</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35998,7 +35999,7 @@
         <v>45968</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36071,7 +36072,7 @@
         <v>45841</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36144,7 +36145,7 @@
         <v>45841</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36217,7 +36218,7 @@
         <v>45666</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36290,7 +36291,7 @@
         <v>45035</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36363,7 +36364,7 @@
         <v>45846</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36436,7 +36437,7 @@
         <v>45573</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36509,7 +36510,7 @@
         <v>45158</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36582,7 +36583,7 @@
         <v>45974</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36655,7 +36656,7 @@
         <v>45282</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36728,7 +36729,7 @@
         <v>45189</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36801,7 +36802,7 @@
         <v>45784</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36874,7 +36875,7 @@
         <v>45239</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36947,7 +36948,7 @@
         <v>45974</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37020,7 +37021,7 @@
         <v>45974</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37093,7 +37094,7 @@
         <v>45606</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37166,7 +37167,7 @@
         <v>45247</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37239,7 +37240,7 @@
         <v>45663</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37312,7 +37313,7 @@
         <v>45691</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37385,7 +37386,7 @@
         <v>45461</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37458,7 +37459,7 @@
         <v>45856</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37531,7 +37532,7 @@
         <v>45190</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37604,7 +37605,7 @@
         <v>45600</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37677,7 +37678,7 @@
         <v>45227</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37750,7 +37751,7 @@
         <v>45862</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37823,7 +37824,7 @@
         <v>44847</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37896,7 +37897,7 @@
         <v>45866</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37969,7 +37970,7 @@
         <v>45866</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38042,7 +38043,7 @@
         <v>45868</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38115,7 +38116,7 @@
         <v>44812</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38188,7 +38189,7 @@
         <v>45225</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38261,7 +38262,7 @@
         <v>45691</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38334,7 +38335,7 @@
         <v>45691</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38407,7 +38408,7 @@
         <v>44565</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38480,7 +38481,7 @@
         <v>44593</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38553,7 +38554,7 @@
         <v>44772</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38626,7 +38627,7 @@
         <v>45257</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38699,7 +38700,7 @@
         <v>45975</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38772,7 +38773,7 @@
         <v>45237</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38845,7 +38846,7 @@
         <v>45357</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38923,7 +38924,7 @@
         <v>45161</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38996,7 +38997,7 @@
         <v>45043</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39069,7 +39070,7 @@
         <v>44810</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39142,7 +39143,7 @@
         <v>45038</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39215,7 +39216,7 @@
         <v>45224</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39288,7 +39289,7 @@
         <v>45163</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39361,7 +39362,7 @@
         <v>45087</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39434,7 +39435,7 @@
         <v>45299</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39507,7 +39508,7 @@
         <v>45745</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39580,7 +39581,7 @@
         <v>45880</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39653,7 +39654,7 @@
         <v>45245</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39726,7 +39727,7 @@
         <v>45281</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39799,7 +39800,7 @@
         <v>45281</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39872,7 +39873,7 @@
         <v>45281</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39945,7 +39946,7 @@
         <v>45237</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40018,7 +40019,7 @@
         <v>45070</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40091,7 +40092,7 @@
         <v>46101</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40164,7 +40165,7 @@
         <v>45223</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40237,7 +40238,7 @@
         <v>45686</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40310,7 +40311,7 @@
         <v>45140</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40383,7 +40384,7 @@
         <v>45008</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40456,7 +40457,7 @@
         <v>45134</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40529,7 +40530,7 @@
         <v>45257</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40602,7 +40603,7 @@
         <v>44515</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40675,7 +40676,7 @@
         <v>45180</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40748,7 +40749,7 @@
         <v>45988</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40821,7 +40822,7 @@
         <v>45992</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40894,7 +40895,7 @@
         <v>45258</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40967,7 +40968,7 @@
         <v>44530</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41040,7 +41041,7 @@
         <v>46112</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41113,7 +41114,7 @@
         <v>44488</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41186,7 +41187,7 @@
         <v>45033</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41259,7 +41260,7 @@
         <v>45994</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41332,7 +41333,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41405,7 +41406,7 @@
         <v>46114</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41478,7 +41479,7 @@
         <v>45538</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41551,7 +41552,7 @@
         <v>45601</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41624,7 +41625,7 @@
         <v>45606</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41697,7 +41698,7 @@
         <v>46118</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41770,7 +41771,7 @@
         <v>44830</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41843,7 +41844,7 @@
         <v>45994</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41916,7 +41917,7 @@
         <v>45994</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41989,7 +41990,7 @@
         <v>45994</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42062,7 +42063,7 @@
         <v>45994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42135,7 +42136,7 @@
         <v>44606</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42208,7 +42209,7 @@
         <v>46121</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42281,7 +42282,7 @@
         <v>45996</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42354,7 +42355,7 @@
         <v>44566</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42427,7 +42428,7 @@
         <v>46125</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42500,7 +42501,7 @@
         <v>45999</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42573,7 +42574,7 @@
         <v>46001</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42646,7 +42647,7 @@
         <v>45008</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42719,7 +42720,7 @@
         <v>45384</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42792,7 +42793,7 @@
         <v>44762</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42865,7 +42866,7 @@
         <v>46128</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42943,7 +42944,7 @@
         <v>44678</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43016,7 +43017,7 @@
         <v>46128</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43094,7 +43095,7 @@
         <v>46001</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43167,7 +43168,7 @@
         <v>44497</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43240,7 +43241,7 @@
         <v>45607</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43313,7 +43314,7 @@
         <v>45395</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43386,7 +43387,7 @@
         <v>45924</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43459,7 +43460,7 @@
         <v>45139</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43532,7 +43533,7 @@
         <v>44896</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43605,7 +43606,7 @@
         <v>45071</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43678,7 +43679,7 @@
         <v>45091</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43751,7 +43752,7 @@
         <v>45558</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43824,7 +43825,7 @@
         <v>45009</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43897,7 +43898,7 @@
         <v>45895</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43970,7 +43971,7 @@
         <v>46009</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44043,7 +44044,7 @@
         <v>45701</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44121,7 +44122,7 @@
         <v>45691</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44194,7 +44195,7 @@
         <v>45715</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44272,7 +44273,7 @@
         <v>45361</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44345,7 +44346,7 @@
         <v>45698</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44418,7 +44419,7 @@
         <v>45699</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44491,7 +44492,7 @@
         <v>45603</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44564,7 +44565,7 @@
         <v>45603</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44637,7 +44638,7 @@
         <v>45688</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44710,7 +44711,7 @@
         <v>45691</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44783,7 +44784,7 @@
         <v>45726</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44856,7 +44857,7 @@
         <v>45043</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44929,7 +44930,7 @@
         <v>44760</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45002,7 +45003,7 @@
         <v>44967</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45075,7 +45076,7 @@
         <v>44967</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45148,7 +45149,7 @@
         <v>45625</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45221,7 +45222,7 @@
         <v>46029</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45294,7 +45295,7 @@
         <v>46030</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45367,7 +45368,7 @@
         <v>44514</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45440,7 +45441,7 @@
         <v>45947</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45513,7 +45514,7 @@
         <v>46030</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45586,7 +45587,7 @@
         <v>45601</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45659,7 +45660,7 @@
         <v>45071</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45732,7 +45733,7 @@
         <v>44945</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45805,7 +45806,7 @@
         <v>46140</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45878,7 +45879,7 @@
         <v>45104</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45951,7 +45952,7 @@
         <v>45320</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46024,7 +46025,7 @@
         <v>45565</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46097,7 +46098,7 @@
         <v>45231</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46170,7 +46171,7 @@
         <v>46041</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46243,7 +46244,7 @@
         <v>44517</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46316,7 +46317,7 @@
         <v>45196</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46389,7 +46390,7 @@
         <v>44613</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46467,7 +46468,7 @@
         <v>45120</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46540,7 +46541,7 @@
         <v>45835</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46613,7 +46614,7 @@
         <v>45237</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46686,7 +46687,7 @@
         <v>44636</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46759,7 +46760,7 @@
         <v>45826</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46832,7 +46833,7 @@
         <v>45533</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46905,7 +46906,7 @@
         <v>45258</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46978,7 +46979,7 @@
         <v>46048</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47051,7 +47052,7 @@
         <v>45797</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47129,7 +47130,7 @@
         <v>45246</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47202,7 +47203,7 @@
         <v>45992</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47275,7 +47276,7 @@
         <v>45163</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47348,7 +47349,7 @@
         <v>45597</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47421,7 +47422,7 @@
         <v>45272</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47494,7 +47495,7 @@
         <v>46048</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47567,7 +47568,7 @@
         <v>46049</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47640,7 +47641,7 @@
         <v>45089</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47713,7 +47714,7 @@
         <v>46101</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47786,7 +47787,7 @@
         <v>44971</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47859,7 +47860,7 @@
         <v>46055</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47932,7 +47933,7 @@
         <v>46062</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48005,7 +48006,7 @@
         <v>46146</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48078,7 +48079,7 @@
         <v>46150</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48151,7 +48152,7 @@
         <v>46071</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48224,7 +48225,7 @@
         <v>46071</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48297,7 +48298,7 @@
         <v>46077</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48370,7 +48371,7 @@
         <v>46063</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48443,7 +48444,7 @@
         <v>46063</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48516,7 +48517,7 @@
         <v>46063</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48589,7 +48590,7 @@
         <v>46087</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48662,7 +48663,7 @@
         <v>46091</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48735,7 +48736,7 @@
         <v>45961</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48808,7 +48809,7 @@
         <v>46168</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48881,7 +48882,7 @@
         <v>46125</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48954,7 +48955,7 @@
         <v>45771</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49027,7 +49028,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49100,7 +49101,7 @@
         <v>46181</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49173,7 +49174,7 @@
         <v>46182</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49251,7 +49252,7 @@
         <v>46182</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49329,7 +49330,7 @@
         <v>46191</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49402,7 +49403,7 @@
         <v>46190</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49475,7 +49476,7 @@
         <v>46206</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49548,7 +49549,7 @@
         <v>46211</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49621,7 +49622,7 @@
         <v>46211</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49694,7 +49695,7 @@
         <v>46216</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49767,7 +49768,7 @@
         <v>46216</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49840,7 +49841,7 @@
         <v>46216</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49913,7 +49914,7 @@
         <v>46223</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49991,7 +49992,7 @@
         <v>46223</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50064,7 +50065,7 @@
         <v>46223</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50142,7 +50143,7 @@
         <v>46224</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50220,7 +50221,7 @@
         <v>46224</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50293,7 +50294,7 @@
         <v>46224</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50366,7 +50367,7 @@
         <v>46267</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50439,7 +50440,7 @@
         <v>46272</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50512,7 +50513,7 @@
         <v>46227</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50585,7 +50586,7 @@
         <v>46268</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50658,7 +50659,7 @@
         <v>45934</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50731,7 +50732,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50804,7 +50805,7 @@
         <v>46271</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50877,7 +50878,7 @@
         <v>46271</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50950,7 +50951,7 @@
         <v>46272</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51023,7 +51024,7 @@
         <v>46231</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51096,7 +51097,7 @@
         <v>46274</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51169,7 +51170,7 @@
         <v>46135</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51242,7 +51243,7 @@
         <v>46232</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51315,7 +51316,7 @@
         <v>46277</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51388,7 +51389,7 @@
         <v>46277</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51461,7 +51462,7 @@
         <v>46238</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51534,7 +51535,7 @@
         <v>46277</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51607,7 +51608,7 @@
         <v>46240</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51680,7 +51681,7 @@
         <v>46245</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51753,7 +51754,7 @@
         <v>45939</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51826,7 +51827,7 @@
         <v>46247</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51899,7 +51900,7 @@
         <v>46057</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51972,7 +51973,7 @@
         <v>45598</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52045,7 +52046,7 @@
         <v>46248</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52118,7 +52119,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52191,7 +52192,7 @@
         <v>46294</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52264,7 +52265,7 @@
         <v>46293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52337,7 +52338,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52410,7 +52411,7 @@
         <v>46253</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52483,7 +52484,7 @@
         <v>46297</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52556,7 +52557,7 @@
         <v>46300</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52629,7 +52630,7 @@
         <v>46255</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52702,7 +52703,7 @@
         <v>46297</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52775,7 +52776,7 @@
         <v>46300</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52853,7 +52854,7 @@
         <v>46300</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52931,7 +52932,7 @@
         <v>45898</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53009,7 +53010,7 @@
         <v>46297</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53082,7 +53083,7 @@
         <v>46255</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53155,7 +53156,7 @@
         <v>46255</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53228,7 +53229,7 @@
         <v>46255</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53301,7 +53302,7 @@
         <v>45939</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53374,7 +53375,7 @@
         <v>46300</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53447,7 +53448,7 @@
         <v>46262</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53520,7 +53521,7 @@
         <v>46261</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53593,7 +53594,7 @@
         <v>46261</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53666,7 +53667,7 @@
         <v>46261</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53739,7 +53740,7 @@
         <v>44658</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53812,7 +53813,7 @@
         <v>45400</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53885,7 +53886,7 @@
         <v>44854</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53958,7 +53959,7 @@
         <v>44771</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54031,7 +54032,7 @@
         <v>45169</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54104,7 +54105,7 @@
         <v>44747</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54177,7 +54178,7 @@
         <v>44960</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54250,7 +54251,7 @@
         <v>44503</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54323,7 +54324,7 @@
         <v>45714</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54396,7 +54397,7 @@
         <v>45171</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54469,7 +54470,7 @@
         <v>46066</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>44481</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>44690</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>45357</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>46083</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>46097</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>46083</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44585</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>45561</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>46097</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>46097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45264</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>45351</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45231</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>45779</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>45806</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>45806</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>45236</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>45264</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45603</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>45134</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>45603</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>44971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45385</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45086</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45876</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45299</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45675</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>46109</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44512</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44553</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>46001</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45568</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44768</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45621</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>46073</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46097</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>46217</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>46223</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>46294</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44498</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>45351</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44861</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>44679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>44512</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>44512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44533</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44531</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44606</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>44817</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44655</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>44809</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44823</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44713</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44565</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44882</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44552</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44491</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44750</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44506</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44621</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44606</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44732</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44657</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44524</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>44854</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>44776</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>44775</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44655</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>44593</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44852</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44656</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44609</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44663</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44532</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44594</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>44480</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44624</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44609</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44881</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45075</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45407</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44880</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45153</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45090</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>45162</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44771</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45626</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45626</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45085</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45085</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>45376</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45357</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45252</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45415</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>44817</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45086</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45471</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45482</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44512</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>45518</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45344</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45215</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44858</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45544</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>45398</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45250</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45428</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>45093</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>45395</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45582</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45239</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45683</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45246</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>45775</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45104</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>45006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         <v>45203</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>45590</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13249,7 +13249,7 @@
         <v>45474</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45443</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>44809</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>45071</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>45321</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>44916</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45002</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44959</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45227</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45227</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45124</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45140</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45608</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44970</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45363</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45242</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45224</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45086</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45112</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45075</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45663</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45362</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45552</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45552</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45412</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45265</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45265</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45320</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45209</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44800</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45181</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45015</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45356</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45159</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45281</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45467</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45320</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45163</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44887</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45593</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45162</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44929</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44697</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44944</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44578</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45168</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45168</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45273</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45161</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45261</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45795</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45735</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45484</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45750</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45484</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45363</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45162</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45408</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44895</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>44947</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45070</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44914</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45889</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45889</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45895</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45895</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45273</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45341</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45677</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45379</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45605</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45357</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45259</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45578</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45901</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45629</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45603</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45408</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45636</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44873</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45771</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>44971</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45332</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45072</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45604</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>44656</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45498</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45157</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45905</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45626</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45338</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>45134</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45909</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21158,7 +21158,7 @@
         <v>45180</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45086</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45231</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45742</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45782</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45643</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>45097</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>45227</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44909</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45362</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45399</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45784</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45354</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45187</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45412</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45553</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45553</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>45043</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>45785</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44638</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>45343</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45324</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45918</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44626</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>45348</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44881</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45163</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>44971</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45709</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44501</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>44672</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>45922</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45922</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>45162</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45923</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45790</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45659</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45585</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45621</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45926</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45041</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45607</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45157</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45059</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45059</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45791</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44663</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45377</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45377</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45377</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45471</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45558</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45573</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45385</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44558</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45191</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>45328</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45324</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45324</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45343</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>44607</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>44607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45547</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45547</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45547</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45933</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>44945</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45934</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45934</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45934</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>45281</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44763</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44663</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>44724</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45412</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45244</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45603</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45316</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45799</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45933</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45225</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45181</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45934</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45344</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45173</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45166</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45937</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45225</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45806</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45806</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45070</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45201</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45938</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45938</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45194</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45194</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>45806</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45166</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45166</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44642</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>44959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45166</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>44638</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44638</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45473</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45231</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45691</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45132</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45199</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45427</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45187</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45560</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45553</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45427</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45939</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45098</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45427</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45666</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45676</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>44735</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45070</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45166</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>44911</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45411</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45710</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45140</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>45140</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45140</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>44845</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>44658</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44831</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45626</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45626</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45626</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>45212</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44908</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>45225</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45225</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45299</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44965</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45233</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45314</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45947</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45824</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>44971</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32236,7 +32236,7 @@
         <v>45681</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45611</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45951</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>45363</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45826</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32601,7 +32601,7 @@
         <v>45720</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>45743</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45730</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45727</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45727</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>45236</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>45236</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45951</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45954</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45954</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45602</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33409,7 +33409,7 @@
         <v>45960</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33482,7 +33482,7 @@
         <v>45960</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>45959</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>45960</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45960</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>45411</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33847,7 +33847,7 @@
         <v>45411</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45197</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45244</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45211</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45833</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45833</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34290,7 +34290,7 @@
         <v>45685</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>45474</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45838</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45835</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45835</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45835</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45838</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>44685</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44503</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45835</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45838</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45835</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>45006</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45838</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45838</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45966</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>45162</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45966</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45838</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45140</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45664</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45838</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>44824</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45968</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45841</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45841</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45666</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45035</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>45846</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>45573</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45158</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45974</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45282</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45189</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45784</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45239</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45974</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37021,7 +37021,7 @@
         <v>45974</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37094,7 +37094,7 @@
         <v>45606</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>45247</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37240,7 +37240,7 @@
         <v>45663</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>45691</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45461</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37459,7 +37459,7 @@
         <v>45856</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45190</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45600</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45227</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45862</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44847</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>45866</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45866</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>45868</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>44812</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45225</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45691</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45691</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44565</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>44593</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44772</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38627,7 +38627,7 @@
         <v>45257</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38700,7 +38700,7 @@
         <v>45975</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45237</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45357</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>45161</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45043</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>44810</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>45038</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45224</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45163</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45087</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45299</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45745</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>45880</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45245</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45281</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45281</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>45281</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45237</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45070</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>46101</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45223</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>45686</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45140</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>45008</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45134</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45257</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>44515</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45180</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>45988</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45992</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45258</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>44530</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>46112</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>44488</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>45033</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41260,7 +41260,7 @@
         <v>45994</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>46114</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45538</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45601</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41625,7 +41625,7 @@
         <v>45606</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46118</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>44830</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45994</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45994</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41990,7 +41990,7 @@
         <v>45994</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45994</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>44606</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>46121</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>45996</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>44566</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>46125</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45999</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>46001</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42647,7 +42647,7 @@
         <v>45008</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45384</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44762</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>46128</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42944,7 +42944,7 @@
         <v>44678</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>46128</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>46001</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44497</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>45607</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45395</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45924</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45139</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>44896</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45071</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45091</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45558</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45009</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45895</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46009</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45701</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45691</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45715</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45361</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45698</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>45699</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45603</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44565,7 +44565,7 @@
         <v>45603</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45688</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44711,7 +44711,7 @@
         <v>45691</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44784,7 +44784,7 @@
         <v>45726</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45043</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>44760</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44967</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>44967</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45149,7 +45149,7 @@
         <v>45625</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>46029</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45295,7 +45295,7 @@
         <v>46030</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>44514</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>45947</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46030</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45587,7 +45587,7 @@
         <v>45601</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45071</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>44945</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>46140</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45879,7 +45879,7 @@
         <v>45104</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45320</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46025,7 +46025,7 @@
         <v>45565</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45231</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46041</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>44517</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45196</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>44613</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45120</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45835</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>45237</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>44636</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45826</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>45533</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46906,7 +46906,7 @@
         <v>45258</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>46048</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>45797</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45246</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>45992</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45163</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45597</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>45272</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>46048</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>46049</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47641,7 +47641,7 @@
         <v>45089</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>46101</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44971</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>46055</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47933,7 +47933,7 @@
         <v>46062</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>46146</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>46150</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>46071</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>46071</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>46077</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>46063</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48444,7 +48444,7 @@
         <v>46063</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>46063</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>46087</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>46091</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45961</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>46168</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>46125</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48955,7 +48955,7 @@
         <v>45771</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>46181</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>46182</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>46182</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>46191</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>46190</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>46206</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>46211</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>46211</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49695,7 +49695,7 @@
         <v>46216</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49768,7 +49768,7 @@
         <v>46216</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>46216</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>46223</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>46223</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>46223</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46224</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>46224</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>46224</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50367,7 +50367,7 @@
         <v>46267</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50440,7 +50440,7 @@
         <v>46272</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>46227</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>46268</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>45934</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46272</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>46271</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>46271</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>46272</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>46231</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>46274</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46135</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>46232</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>46277</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51389,7 +51389,7 @@
         <v>46277</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51462,7 +51462,7 @@
         <v>46238</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51535,7 +51535,7 @@
         <v>46277</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>46240</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>46245</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45939</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>46247</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>46057</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>45598</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46248</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52192,7 +52192,7 @@
         <v>46294</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>46293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>46293</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>46253</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52484,7 +52484,7 @@
         <v>46297</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52557,7 +52557,7 @@
         <v>46300</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52630,7 +52630,7 @@
         <v>46255</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>46297</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>46300</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52854,7 +52854,7 @@
         <v>46300</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45898</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53010,7 +53010,7 @@
         <v>46297</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53083,7 +53083,7 @@
         <v>46255</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53156,7 +53156,7 @@
         <v>46255</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
         <v>46255</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45939</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46300</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>46262</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>46261</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53594,7 +53594,7 @@
         <v>46261</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53667,7 +53667,7 @@
         <v>46261</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44658</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>45400</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>44854</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53959,7 +53959,7 @@
         <v>44771</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45169</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>44747</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>44960</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54251,7 +54251,7 @@
         <v>44503</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>45714</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>45171</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>46066</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -617,13 +617,13 @@
         <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -638,19 +638,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -658,6 +658,7 @@
 Skogsalm
 Brunfläckig pärlemorfjäril
 Drillsnäppa
+Entita
 Järnsparv
 Mindre tåtelsmygare
 Hagfingersvamp
@@ -732,7 +733,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +841,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +949,7 @@
         <v>44690</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1061,7 @@
         <v>45357</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1172,7 +1173,7 @@
         <v>46083</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1284,7 +1285,7 @@
         <v>46097</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1396,7 +1397,7 @@
         <v>46083</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1508,7 +1509,7 @@
         <v>44585</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1615,7 @@
         <v>45561</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1724,7 +1725,7 @@
         <v>46097</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1835,7 +1836,7 @@
         <v>45785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1941,7 +1942,7 @@
         <v>46097</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2053,7 @@
         <v>44872</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2158,7 @@
         <v>44879</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2263,7 @@
         <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2372,7 +2373,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2477,7 +2478,7 @@
         <v>45675</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2583,7 @@
         <v>45351</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2688,7 @@
         <v>45134</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2793,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2897,7 +2898,7 @@
         <v>45086</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3003,7 @@
         <v>44512</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3107,7 +3108,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3212,7 +3213,7 @@
         <v>45621</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3317,7 +3318,7 @@
         <v>45895</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,7 +3423,7 @@
         <v>45264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3527,7 +3528,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,7 +3637,7 @@
         <v>46001</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3741,7 +3742,7 @@
         <v>45236</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3846,7 +3847,7 @@
         <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3955,7 +3956,7 @@
         <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4066,7 @@
         <v>45568</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4170,7 +4171,7 @@
         <v>46109</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4275,7 +4276,7 @@
         <v>44553</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4380,7 +4381,7 @@
         <v>46217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4485,7 +4486,7 @@
         <v>46223</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4595,7 +4596,7 @@
         <v>44971</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4700,7 +4701,7 @@
         <v>46294</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4809,7 +4810,7 @@
         <v>45231</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4919,7 @@
         <v>45779</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5023,7 +5024,7 @@
         <v>45806</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5132,7 +5133,7 @@
         <v>45806</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5241,7 +5242,7 @@
         <v>45264</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5346,7 +5347,7 @@
         <v>45876</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5451,7 +5452,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5556,7 +5557,7 @@
         <v>45351</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5661,7 +5662,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5734,7 +5735,7 @@
         <v>44861</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5807,7 +5808,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5880,7 +5881,7 @@
         <v>44679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5953,7 +5954,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6026,7 +6027,7 @@
         <v>44512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6104,7 +6105,7 @@
         <v>44533</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6177,7 +6178,7 @@
         <v>44531</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6250,7 +6251,7 @@
         <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6323,7 +6324,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6396,7 +6397,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6469,7 +6470,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6542,7 +6543,7 @@
         <v>44636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6615,7 +6616,7 @@
         <v>44655</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6688,7 +6689,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6761,7 +6762,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6834,7 +6835,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6907,7 +6908,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6980,7 +6981,7 @@
         <v>44533</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7053,7 +7054,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7126,7 +7127,7 @@
         <v>44713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7199,7 +7200,7 @@
         <v>44497</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7272,7 +7273,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7345,7 +7346,7 @@
         <v>44882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7418,7 +7419,7 @@
         <v>44552</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7491,7 +7492,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7564,7 +7565,7 @@
         <v>44506</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7637,7 +7638,7 @@
         <v>44732</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7710,7 +7711,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7788,7 +7789,7 @@
         <v>44657</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7861,7 +7862,7 @@
         <v>44854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7934,7 +7935,7 @@
         <v>44776</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8007,7 +8008,7 @@
         <v>44775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8080,7 +8081,7 @@
         <v>44655</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8153,7 +8154,7 @@
         <v>44852</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8226,7 +8227,7 @@
         <v>44733</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8299,7 +8300,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8372,7 +8373,7 @@
         <v>44656</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8445,7 +8446,7 @@
         <v>44594</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8518,7 +8519,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8591,7 +8592,7 @@
         <v>44509</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8664,7 +8665,7 @@
         <v>44868</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8737,7 +8738,7 @@
         <v>44663</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8810,7 +8811,7 @@
         <v>44882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8883,7 +8884,7 @@
         <v>44621</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8956,7 +8957,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9029,7 +9030,7 @@
         <v>44524</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9102,7 +9103,7 @@
         <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9175,7 +9176,7 @@
         <v>44609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9248,7 +9249,7 @@
         <v>44593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9321,7 +9322,7 @@
         <v>44638</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9394,7 +9395,7 @@
         <v>44624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9467,7 +9468,7 @@
         <v>44609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9540,7 +9541,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9613,7 +9614,7 @@
         <v>44760</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9686,7 +9687,7 @@
         <v>44772</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9759,7 +9760,7 @@
         <v>44945</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9832,7 +9833,7 @@
         <v>45412</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9905,7 +9906,7 @@
         <v>45180</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9978,7 +9979,7 @@
         <v>45348</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10051,7 +10052,7 @@
         <v>44959</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10124,7 +10125,7 @@
         <v>45553</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10197,7 +10198,7 @@
         <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10270,7 +10271,7 @@
         <v>44881</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10343,7 +10344,7 @@
         <v>45585</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10416,7 +10417,7 @@
         <v>45681</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10489,7 +10490,7 @@
         <v>44831</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10562,7 +10563,7 @@
         <v>44512</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10640,7 +10641,7 @@
         <v>45162</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10713,7 +10714,7 @@
         <v>45093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10786,7 +10787,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10859,7 +10860,7 @@
         <v>45162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10932,7 +10933,7 @@
         <v>45357</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11005,7 +11006,7 @@
         <v>44959</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11078,7 +11079,7 @@
         <v>45211</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11151,7 +11152,7 @@
         <v>45602</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11224,7 +11225,7 @@
         <v>44724</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11297,7 +11298,7 @@
         <v>44895</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11370,7 +11371,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11443,7 +11444,7 @@
         <v>45344</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11516,7 +11517,7 @@
         <v>45124</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11589,7 +11590,7 @@
         <v>44894</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11662,7 +11663,7 @@
         <v>44578</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11735,7 +11736,7 @@
         <v>45006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11813,7 +11814,7 @@
         <v>45314</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11886,7 +11887,7 @@
         <v>45237</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11959,7 +11960,7 @@
         <v>45201</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12032,7 +12033,7 @@
         <v>45247</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12105,7 +12106,7 @@
         <v>45558</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12178,7 +12179,7 @@
         <v>45321</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12251,7 +12252,7 @@
         <v>45376</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12324,7 +12325,7 @@
         <v>45357</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12402,7 +12403,7 @@
         <v>45363</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12475,7 +12476,7 @@
         <v>45691</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12548,7 +12549,7 @@
         <v>45606</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12621,7 +12622,7 @@
         <v>44959</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12694,7 +12695,7 @@
         <v>45265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12767,7 +12768,7 @@
         <v>45265</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12840,7 +12841,7 @@
         <v>45070</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12913,7 +12914,7 @@
         <v>45181</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12986,7 +12987,7 @@
         <v>45227</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13059,7 +13060,7 @@
         <v>44916</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13132,7 +13133,7 @@
         <v>44916</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13205,7 +13206,7 @@
         <v>45162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13278,7 +13279,7 @@
         <v>45162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13351,7 +13352,7 @@
         <v>45140</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13424,7 +13425,7 @@
         <v>45482</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13497,7 +13498,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13570,7 +13571,7 @@
         <v>45071</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13643,7 +13644,7 @@
         <v>45362</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13721,7 +13722,7 @@
         <v>45224</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13794,7 +13795,7 @@
         <v>45162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13867,7 +13868,7 @@
         <v>45411</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13940,7 +13941,7 @@
         <v>45334</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14013,7 +14014,7 @@
         <v>44566</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14086,7 +14087,7 @@
         <v>44929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14159,7 +14160,7 @@
         <v>44824</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14232,7 +14233,7 @@
         <v>45518</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14305,7 +14306,7 @@
         <v>45399</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14378,7 +14379,7 @@
         <v>45603</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14456,7 +14457,7 @@
         <v>44517</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14529,7 +14530,7 @@
         <v>45666</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14602,7 +14603,7 @@
         <v>45621</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14675,7 +14676,7 @@
         <v>45180</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14748,7 +14749,7 @@
         <v>45196</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14821,7 +14822,7 @@
         <v>45281</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14894,7 +14895,7 @@
         <v>45443</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14967,7 +14968,7 @@
         <v>45467</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15040,7 +15041,7 @@
         <v>44970</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15113,7 +15114,7 @@
         <v>44971</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15186,7 +15187,7 @@
         <v>45683</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15259,7 +15260,7 @@
         <v>45664</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15332,7 +15333,7 @@
         <v>45246</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15405,7 +15406,7 @@
         <v>45685</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15478,7 +15479,7 @@
         <v>45043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15551,7 +15552,7 @@
         <v>45299</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15624,7 +15625,7 @@
         <v>45157</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15697,7 +15698,7 @@
         <v>45606</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15770,7 +15771,7 @@
         <v>45324</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15848,7 +15849,7 @@
         <v>44947</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15921,7 +15922,7 @@
         <v>45227</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15994,7 +15995,7 @@
         <v>45227</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16067,7 +16068,7 @@
         <v>44636</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16140,7 +16141,7 @@
         <v>44873</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16213,7 +16214,7 @@
         <v>44917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16291,7 +16292,7 @@
         <v>45412</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16364,7 +16365,7 @@
         <v>44800</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16437,7 +16438,7 @@
         <v>45259</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16510,7 +16511,7 @@
         <v>45231</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16588,7 +16589,7 @@
         <v>45608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16661,7 +16662,7 @@
         <v>45663</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16734,7 +16735,7 @@
         <v>44663</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16807,7 +16808,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16880,7 +16881,7 @@
         <v>44663</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16953,7 +16954,7 @@
         <v>45075</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17026,7 +17027,7 @@
         <v>44606</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17099,7 +17100,7 @@
         <v>44607</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17172,7 +17173,7 @@
         <v>44607</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17245,7 +17246,7 @@
         <v>44558</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17318,7 +17319,7 @@
         <v>45258</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17391,7 +17392,7 @@
         <v>45194</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17464,7 +17465,7 @@
         <v>45282</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17537,7 +17538,7 @@
         <v>45002</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17610,7 +17611,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17683,7 +17684,7 @@
         <v>45553</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17756,7 +17757,7 @@
         <v>45553</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17829,7 +17830,7 @@
         <v>45281</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17902,7 +17903,7 @@
         <v>45281</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17975,7 +17976,7 @@
         <v>45281</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18048,7 +18049,7 @@
         <v>45239</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18121,7 +18122,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18194,7 +18195,7 @@
         <v>45343</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18267,7 +18268,7 @@
         <v>45191</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18340,7 +18341,7 @@
         <v>45659</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18413,7 +18414,7 @@
         <v>45341</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18486,7 +18487,7 @@
         <v>45361</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18559,7 +18560,7 @@
         <v>45735</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18632,7 +18633,7 @@
         <v>45992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18705,7 +18706,7 @@
         <v>45797</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18783,7 +18784,7 @@
         <v>45159</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18856,7 +18857,7 @@
         <v>45112</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18929,7 +18930,7 @@
         <v>45593</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19002,7 +19003,7 @@
         <v>45895</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19075,7 +19076,7 @@
         <v>44887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19153,7 +19154,7 @@
         <v>45582</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19226,7 +19227,7 @@
         <v>45427</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19299,7 +19300,7 @@
         <v>45889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19372,7 +19373,7 @@
         <v>45889</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19445,7 +19446,7 @@
         <v>45324</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19518,7 +19519,7 @@
         <v>45324</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19596,7 +19597,7 @@
         <v>45889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19669,7 +19670,7 @@
         <v>45795</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19742,7 +19743,7 @@
         <v>45835</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19815,7 +19816,7 @@
         <v>45889</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19888,7 +19889,7 @@
         <v>45895</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19961,7 +19962,7 @@
         <v>45895</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20039,7 +20040,7 @@
         <v>45643</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20112,7 +20113,7 @@
         <v>44638</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20190,7 +20191,7 @@
         <v>44638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20268,7 +20269,7 @@
         <v>45896</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20341,7 +20342,7 @@
         <v>45896</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20414,7 +20415,7 @@
         <v>45924</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20487,7 +20488,7 @@
         <v>45636</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20560,7 +20561,7 @@
         <v>45826</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20633,7 +20634,7 @@
         <v>45231</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20706,7 +20707,7 @@
         <v>45162</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20779,7 +20780,7 @@
         <v>44894</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20852,7 +20853,7 @@
         <v>45252</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20925,7 +20926,7 @@
         <v>46101</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20998,7 +20999,7 @@
         <v>45354</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21071,7 +21072,7 @@
         <v>45901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21144,7 +21145,7 @@
         <v>45771</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21217,7 +21218,7 @@
         <v>45233</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21290,7 +21291,7 @@
         <v>45085</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21363,7 +21364,7 @@
         <v>45085</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21436,7 +21437,7 @@
         <v>45484</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21509,7 +21510,7 @@
         <v>45343</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21582,7 +21583,7 @@
         <v>45089</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21655,7 +21656,7 @@
         <v>44636</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21728,7 +21729,7 @@
         <v>45905</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21801,7 +21802,7 @@
         <v>46140</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21874,7 +21875,7 @@
         <v>45187</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21947,7 +21948,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22020,7 +22021,7 @@
         <v>45611</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22093,7 +22094,7 @@
         <v>45909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22166,7 +22167,7 @@
         <v>45909</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22239,7 +22240,7 @@
         <v>45362</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22317,7 +22318,7 @@
         <v>45043</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22390,7 +22391,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22463,7 +22464,7 @@
         <v>45742</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22536,7 +22537,7 @@
         <v>45547</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22614,7 +22615,7 @@
         <v>45547</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22692,7 +22693,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22770,7 +22771,7 @@
         <v>45075</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22843,7 +22844,7 @@
         <v>44945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22916,7 +22917,7 @@
         <v>46146</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22989,7 +22990,7 @@
         <v>45035</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23062,7 +23063,7 @@
         <v>45918</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23135,7 +23136,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23208,7 +23209,7 @@
         <v>45320</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23281,7 +23282,7 @@
         <v>45922</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23354,7 +23355,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23427,7 +23428,7 @@
         <v>45134</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23500,7 +23501,7 @@
         <v>45923</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23573,7 +23574,7 @@
         <v>44911</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23646,7 +23647,7 @@
         <v>44908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23719,7 +23720,7 @@
         <v>45162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23792,7 +23793,7 @@
         <v>45104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23865,7 +23866,7 @@
         <v>45926</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23938,7 +23939,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24011,7 +24012,7 @@
         <v>45933</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24084,7 +24085,7 @@
         <v>45933</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24157,7 +24158,7 @@
         <v>45934</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24230,7 +24231,7 @@
         <v>45934</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24303,7 +24304,7 @@
         <v>45934</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24376,7 +24377,7 @@
         <v>45934</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24449,7 +24450,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24522,7 +24523,7 @@
         <v>46150</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24595,7 +24596,7 @@
         <v>45173</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24668,7 +24669,7 @@
         <v>45937</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24741,7 +24742,7 @@
         <v>45261</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24814,7 +24815,7 @@
         <v>45939</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24887,7 +24888,7 @@
         <v>45411</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24960,7 +24961,7 @@
         <v>45411</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25033,7 +25034,7 @@
         <v>45938</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25106,7 +25107,7 @@
         <v>45938</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25179,7 +25180,7 @@
         <v>44656</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25252,7 +25253,7 @@
         <v>45939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25325,7 +25326,7 @@
         <v>44881</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25398,7 +25399,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25471,7 +25472,7 @@
         <v>44762</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25544,7 +25545,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25617,7 +25618,7 @@
         <v>44514</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25690,7 +25691,7 @@
         <v>45203</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25763,7 +25764,7 @@
         <v>45947</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25836,7 +25837,7 @@
         <v>45237</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25909,7 +25910,7 @@
         <v>45677</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25982,7 +25983,7 @@
         <v>45951</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26055,7 +26056,7 @@
         <v>45087</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26128,7 +26129,7 @@
         <v>45258</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26201,7 +26202,7 @@
         <v>45951</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26274,7 +26275,7 @@
         <v>45578</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26347,7 +26348,7 @@
         <v>45954</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26420,7 +26421,7 @@
         <v>45415</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26493,7 +26494,7 @@
         <v>45710</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26566,7 +26567,7 @@
         <v>45954</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26644,7 +26645,7 @@
         <v>45344</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26717,7 +26718,7 @@
         <v>44678</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26790,7 +26791,7 @@
         <v>45258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26863,7 +26864,7 @@
         <v>45474</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26936,7 +26937,7 @@
         <v>45959</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27009,7 +27010,7 @@
         <v>45960</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27082,7 +27083,7 @@
         <v>45086</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27155,7 +27156,7 @@
         <v>45960</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27228,7 +27229,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27301,7 +27302,7 @@
         <v>45960</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27374,7 +27375,7 @@
         <v>44944</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27447,7 +27448,7 @@
         <v>45960</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27520,7 +27521,7 @@
         <v>45008</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27593,7 +27594,7 @@
         <v>45153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27666,7 +27667,7 @@
         <v>45966</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27739,7 +27740,7 @@
         <v>45966</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27812,7 +27813,7 @@
         <v>45605</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27885,7 +27886,7 @@
         <v>45237</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27958,7 +27959,7 @@
         <v>45006</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28036,7 +28037,7 @@
         <v>45968</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28109,7 +28110,7 @@
         <v>45974</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28182,7 +28183,7 @@
         <v>45975</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28255,7 +28256,7 @@
         <v>44971</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28328,7 +28329,7 @@
         <v>45974</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28401,7 +28402,7 @@
         <v>45974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28474,7 +28475,7 @@
         <v>44781</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28547,7 +28548,7 @@
         <v>45626</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28620,7 +28621,7 @@
         <v>45626</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28693,7 +28694,7 @@
         <v>45666</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28766,7 +28767,7 @@
         <v>45236</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28839,7 +28840,7 @@
         <v>45236</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28912,7 +28913,7 @@
         <v>45194</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28985,7 +28986,7 @@
         <v>45140</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29058,7 +29059,7 @@
         <v>45140</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29131,7 +29132,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29204,7 +29205,7 @@
         <v>45607</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29277,7 +29278,7 @@
         <v>44809</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29350,7 +29351,7 @@
         <v>45281</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29423,7 +29424,7 @@
         <v>45189</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29496,7 +29497,7 @@
         <v>45097</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29569,7 +29570,7 @@
         <v>45273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29642,7 +29643,7 @@
         <v>44638</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29720,7 +29721,7 @@
         <v>45686</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29793,7 +29794,7 @@
         <v>45988</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29866,7 +29867,7 @@
         <v>45395</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29939,7 +29940,7 @@
         <v>45992</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30012,7 +30013,7 @@
         <v>46168</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30085,7 +30086,7 @@
         <v>45163</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30158,7 +30159,7 @@
         <v>45560</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30231,7 +30232,7 @@
         <v>45994</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30304,7 +30305,7 @@
         <v>45994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30377,7 +30378,7 @@
         <v>45994</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30450,7 +30451,7 @@
         <v>45994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30523,7 +30524,7 @@
         <v>45994</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30596,7 +30597,7 @@
         <v>45994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30669,7 +30670,7 @@
         <v>45698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30742,7 +30743,7 @@
         <v>45996</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30815,7 +30816,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30888,7 +30889,7 @@
         <v>46001</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30961,7 +30962,7 @@
         <v>45533</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31034,7 +31035,7 @@
         <v>45223</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31107,7 +31108,7 @@
         <v>46001</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31180,7 +31181,7 @@
         <v>45140</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31253,7 +31254,7 @@
         <v>45603</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31331,7 +31332,7 @@
         <v>45626</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31404,7 +31405,7 @@
         <v>46125</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31477,7 +31478,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31550,7 +31551,7 @@
         <v>46009</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31623,7 +31624,7 @@
         <v>45691</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31696,7 +31697,7 @@
         <v>44626</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31769,7 +31770,7 @@
         <v>45691</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31842,7 +31843,7 @@
         <v>45771</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31915,7 +31916,7 @@
         <v>45698</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31988,7 +31989,7 @@
         <v>44914</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32061,7 +32062,7 @@
         <v>45715</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32139,7 +32140,7 @@
         <v>45726</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32212,7 +32213,7 @@
         <v>45688</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32285,7 +32286,7 @@
         <v>45699</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32358,7 +32359,7 @@
         <v>45701</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32436,7 +32437,7 @@
         <v>45603</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32509,7 +32510,7 @@
         <v>45603</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32582,7 +32583,7 @@
         <v>45043</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32655,7 +32656,7 @@
         <v>45398</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32728,7 +32729,7 @@
         <v>44971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32801,7 +32802,7 @@
         <v>44515</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32874,7 +32875,7 @@
         <v>45199</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32947,7 +32948,7 @@
         <v>46029</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33020,7 +33021,7 @@
         <v>45071</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33093,7 +33094,7 @@
         <v>45427</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33166,7 +33167,7 @@
         <v>45166</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33239,7 +33240,7 @@
         <v>44830</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33312,7 +33313,7 @@
         <v>45691</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33385,7 +33386,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33458,7 +33459,7 @@
         <v>46030</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33531,7 +33532,7 @@
         <v>44965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33604,7 +33605,7 @@
         <v>46041</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33677,7 +33678,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33750,7 +33751,7 @@
         <v>46182</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33828,7 +33829,7 @@
         <v>46182</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33906,7 +33907,7 @@
         <v>45356</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33979,7 +33980,7 @@
         <v>45601</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34052,7 +34053,7 @@
         <v>46049</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34125,7 +34126,7 @@
         <v>46048</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34198,7 +34199,7 @@
         <v>46048</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34271,7 +34272,7 @@
         <v>45280</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34344,7 +34345,7 @@
         <v>45498</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34422,7 +34423,7 @@
         <v>45197</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34500,7 +34501,7 @@
         <v>45316</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34573,7 +34574,7 @@
         <v>45357</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34651,7 +34652,7 @@
         <v>46055</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34724,7 +34725,7 @@
         <v>45009</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34797,7 +34798,7 @@
         <v>45163</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34870,7 +34871,7 @@
         <v>44530</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34943,7 +34944,7 @@
         <v>46181</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35016,7 +35017,7 @@
         <v>45407</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35089,7 +35090,7 @@
         <v>45471</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35162,7 +35163,7 @@
         <v>44847</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35235,7 +35236,7 @@
         <v>46062</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35308,7 +35309,7 @@
         <v>44812</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35381,7 +35382,7 @@
         <v>44971</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35454,7 +35455,7 @@
         <v>45601</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35527,7 +35528,7 @@
         <v>44685</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35600,7 +35601,7 @@
         <v>46071</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35673,7 +35674,7 @@
         <v>46071</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35746,7 +35747,7 @@
         <v>45538</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35819,7 +35820,7 @@
         <v>45093</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35892,7 +35893,7 @@
         <v>45320</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35965,7 +35966,7 @@
         <v>46077</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36038,7 +36039,7 @@
         <v>46063</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36111,7 +36112,7 @@
         <v>46063</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36184,7 +36185,7 @@
         <v>46063</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36257,7 +36258,7 @@
         <v>44771</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36330,7 +36331,7 @@
         <v>45215</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36403,7 +36404,7 @@
         <v>46190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36476,7 +36477,7 @@
         <v>44817</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36549,7 +36550,7 @@
         <v>45070</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36622,7 +36623,7 @@
         <v>46087</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36695,7 +36696,7 @@
         <v>45671</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36768,7 +36769,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36841,7 +36842,7 @@
         <v>45002</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36914,7 +36915,7 @@
         <v>45484</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36987,7 +36988,7 @@
         <v>46191</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37060,7 +37061,7 @@
         <v>45225</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37133,7 +37134,7 @@
         <v>45625</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37206,7 +37207,7 @@
         <v>45140</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37279,7 +37280,7 @@
         <v>45120</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37352,7 +37353,7 @@
         <v>46101</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37425,7 +37426,7 @@
         <v>45166</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37498,7 +37499,7 @@
         <v>45166</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37571,7 +37572,7 @@
         <v>45166</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37644,7 +37645,7 @@
         <v>46112</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37717,7 +37718,7 @@
         <v>44959</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37790,7 +37791,7 @@
         <v>44959</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37863,7 +37864,7 @@
         <v>46114</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37936,7 +37937,7 @@
         <v>46118</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38009,7 +38010,7 @@
         <v>44882</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38082,7 +38083,7 @@
         <v>45072</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38155,7 +38156,7 @@
         <v>46121</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38228,7 +38229,7 @@
         <v>46125</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38301,7 +38302,7 @@
         <v>44845</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38374,7 +38375,7 @@
         <v>45338</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38447,7 +38448,7 @@
         <v>46128</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38525,7 +38526,7 @@
         <v>46128</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38603,7 +38604,7 @@
         <v>45395</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38676,7 +38677,7 @@
         <v>45676</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38749,7 +38750,7 @@
         <v>45385</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38822,7 +38823,7 @@
         <v>45626</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38895,7 +38896,7 @@
         <v>45626</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38968,7 +38969,7 @@
         <v>45626</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39041,7 +39042,7 @@
         <v>45299</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39114,7 +39115,7 @@
         <v>45181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39187,7 +39188,7 @@
         <v>45320</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39260,7 +39261,7 @@
         <v>45224</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39333,7 +39334,7 @@
         <v>45363</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39406,7 +39407,7 @@
         <v>45166</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39479,7 +39480,7 @@
         <v>45225</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39552,7 +39553,7 @@
         <v>45190</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39625,7 +39626,7 @@
         <v>44501</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39698,7 +39699,7 @@
         <v>45947</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39771,7 +39772,7 @@
         <v>45384</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39844,7 +39845,7 @@
         <v>45163</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39917,7 +39918,7 @@
         <v>45558</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39990,7 +39991,7 @@
         <v>45597</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40063,7 +40064,7 @@
         <v>45565</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40136,7 +40137,7 @@
         <v>45225</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40209,7 +40210,7 @@
         <v>45225</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40282,7 +40283,7 @@
         <v>45250</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40355,7 +40356,7 @@
         <v>45775</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40428,7 +40429,7 @@
         <v>45104</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40501,7 +40502,7 @@
         <v>45008</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40574,7 +40575,7 @@
         <v>44763</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40647,7 +40648,7 @@
         <v>45328</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40720,7 +40721,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40793,7 +40794,7 @@
         <v>45086</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40866,7 +40867,7 @@
         <v>45552</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40939,7 +40940,7 @@
         <v>45552</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41012,7 +41013,7 @@
         <v>46211</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41085,7 +41086,7 @@
         <v>46216</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41158,7 +41159,7 @@
         <v>46216</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41231,7 +41232,7 @@
         <v>46216</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41304,7 +41305,7 @@
         <v>46211</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41377,7 +41378,7 @@
         <v>45139</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41450,7 +41451,7 @@
         <v>45408</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41523,7 +41524,7 @@
         <v>46223</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41596,7 +41597,7 @@
         <v>44735</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41669,7 +41670,7 @@
         <v>46223</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41747,7 +41748,7 @@
         <v>46224</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41820,7 +41821,7 @@
         <v>46224</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41893,7 +41894,7 @@
         <v>46223</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41971,7 +41972,7 @@
         <v>46224</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42049,7 +42050,7 @@
         <v>46227</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42122,7 +42123,7 @@
         <v>46272</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42195,7 +42196,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42268,7 +42269,7 @@
         <v>46272</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42341,7 +42342,7 @@
         <v>45461</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42414,7 +42415,7 @@
         <v>46272</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42487,7 +42488,7 @@
         <v>45573</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42560,7 +42561,7 @@
         <v>46271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42633,7 +42634,7 @@
         <v>46271</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42706,7 +42707,7 @@
         <v>45033</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42779,7 +42780,7 @@
         <v>45934</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42852,7 +42853,7 @@
         <v>45161</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42925,7 +42926,7 @@
         <v>46135</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42998,7 +42999,7 @@
         <v>46231</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43071,7 +43072,7 @@
         <v>45377</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43144,7 +43145,7 @@
         <v>45377</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43217,7 +43218,7 @@
         <v>45377</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43290,7 +43291,7 @@
         <v>46232</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43363,7 +43364,7 @@
         <v>46274</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43436,7 +43437,7 @@
         <v>46277</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43509,7 +43510,7 @@
         <v>46277</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43582,7 +43583,7 @@
         <v>44858</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43655,7 +43656,7 @@
         <v>45363</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43728,7 +43729,7 @@
         <v>45474</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43801,7 +43802,7 @@
         <v>45590</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43874,7 +43875,7 @@
         <v>45573</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43947,7 +43948,7 @@
         <v>45227</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44020,7 +44021,7 @@
         <v>45187</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44093,7 +44094,7 @@
         <v>45257</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44166,7 +44167,7 @@
         <v>46238</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44239,7 +44240,7 @@
         <v>45691</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44312,7 +44313,7 @@
         <v>45408</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44385,7 +44386,7 @@
         <v>46240</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44458,7 +44459,7 @@
         <v>45332</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44531,7 +44532,7 @@
         <v>45134</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44604,7 +44605,7 @@
         <v>44593</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44677,7 +44678,7 @@
         <v>45242</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44750,7 +44751,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44823,7 +44824,7 @@
         <v>46277</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44896,7 +44897,7 @@
         <v>44810</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44969,7 +44970,7 @@
         <v>45427</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45042,7 +45043,7 @@
         <v>45246</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45115,7 +45116,7 @@
         <v>45098</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45188,7 +45189,7 @@
         <v>45272</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45261,7 +45262,7 @@
         <v>45086</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45334,7 +45335,7 @@
         <v>44565</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45407,7 +45408,7 @@
         <v>46245</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45480,7 +45481,7 @@
         <v>45604</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45553,7 +45554,7 @@
         <v>45070</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45626,7 +45627,7 @@
         <v>44642</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45699,7 +45700,7 @@
         <v>45598</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45772,7 +45773,7 @@
         <v>46248</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45845,7 +45846,7 @@
         <v>45273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45918,7 +45919,7 @@
         <v>46057</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45991,7 +45992,7 @@
         <v>45059</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46064,7 +46065,7 @@
         <v>45059</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46137,7 +46138,7 @@
         <v>46293</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46210,7 +46211,7 @@
         <v>45168</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46283,7 +46284,7 @@
         <v>45168</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46356,7 +46357,7 @@
         <v>45038</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46429,7 +46430,7 @@
         <v>46293</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46502,7 +46503,7 @@
         <v>44909</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46575,7 +46576,7 @@
         <v>45750</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46648,7 +46649,7 @@
         <v>45745</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46721,7 +46722,7 @@
         <v>46293</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46794,7 +46795,7 @@
         <v>46247</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46867,7 +46868,7 @@
         <v>45225</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46940,7 +46941,7 @@
         <v>44967</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47013,7 +47014,7 @@
         <v>44967</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47086,7 +47087,7 @@
         <v>45643</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47159,7 +47160,7 @@
         <v>45041</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47232,7 +47233,7 @@
         <v>44497</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47305,7 +47306,7 @@
         <v>45090</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47378,7 +47379,7 @@
         <v>44672</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47451,7 +47452,7 @@
         <v>45209</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47524,7 +47525,7 @@
         <v>46294</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47597,7 +47598,7 @@
         <v>44613</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47675,7 +47676,7 @@
         <v>45544</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47748,7 +47749,7 @@
         <v>45158</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47821,7 +47822,7 @@
         <v>45428</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47894,7 +47895,7 @@
         <v>45070</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47967,7 +47968,7 @@
         <v>45471</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48040,7 +48041,7 @@
         <v>45939</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48113,7 +48114,7 @@
         <v>44658</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48186,7 +48187,7 @@
         <v>44488</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48259,7 +48260,7 @@
         <v>46297</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48332,7 +48333,7 @@
         <v>46297</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48405,7 +48406,7 @@
         <v>46253</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48478,7 +48479,7 @@
         <v>46297</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48551,7 +48552,7 @@
         <v>45015</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48624,7 +48625,7 @@
         <v>45071</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48697,7 +48698,7 @@
         <v>46300</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48770,7 +48771,7 @@
         <v>45898</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48848,7 +48849,7 @@
         <v>46300</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48926,7 +48927,7 @@
         <v>46300</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48999,7 +49000,7 @@
         <v>45231</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49072,7 +49073,7 @@
         <v>46255</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49145,7 +49146,7 @@
         <v>45782</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49218,7 +49219,7 @@
         <v>46255</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49291,7 +49292,7 @@
         <v>45785</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49364,7 +49365,7 @@
         <v>45412</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49437,7 +49438,7 @@
         <v>46255</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49510,7 +49511,7 @@
         <v>46255</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49583,7 +49584,7 @@
         <v>45784</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49656,7 +49657,7 @@
         <v>46300</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49734,7 +49735,7 @@
         <v>45709</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49807,7 +49808,7 @@
         <v>45157</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49880,7 +49881,7 @@
         <v>45791</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49953,7 +49954,7 @@
         <v>45790</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50026,7 +50027,7 @@
         <v>46261</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50099,7 +50100,7 @@
         <v>46262</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50172,7 +50173,7 @@
         <v>46261</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50245,7 +50246,7 @@
         <v>46261</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50318,7 +50319,7 @@
         <v>45797</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50391,7 +50392,7 @@
         <v>45799</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50464,7 +50465,7 @@
         <v>45806</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50537,7 +50538,7 @@
         <v>45806</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50610,7 +50611,7 @@
         <v>45806</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50683,7 +50684,7 @@
         <v>45132</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50756,7 +50757,7 @@
         <v>45473</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50829,7 +50830,7 @@
         <v>46268</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50902,7 +50903,7 @@
         <v>46267</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50975,7 +50976,7 @@
         <v>45212</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51048,7 +51049,7 @@
         <v>45824</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51121,7 +51122,7 @@
         <v>45727</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51194,7 +51195,7 @@
         <v>45727</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51267,7 +51268,7 @@
         <v>45826</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51340,7 +51341,7 @@
         <v>45730</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51413,7 +51414,7 @@
         <v>45743</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51486,7 +51487,7 @@
         <v>45720</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51559,7 +51560,7 @@
         <v>45833</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51632,7 +51633,7 @@
         <v>45835</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51705,7 +51706,7 @@
         <v>45835</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51778,7 +51779,7 @@
         <v>45833</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51851,7 +51852,7 @@
         <v>45835</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51924,7 +51925,7 @@
         <v>45835</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51997,7 +51998,7 @@
         <v>45835</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52070,7 +52071,7 @@
         <v>45838</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52148,7 +52149,7 @@
         <v>45838</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52221,7 +52222,7 @@
         <v>45838</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52299,7 +52300,7 @@
         <v>45838</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52377,7 +52378,7 @@
         <v>45838</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52455,7 +52456,7 @@
         <v>45838</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52533,7 +52534,7 @@
         <v>45838</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52606,7 +52607,7 @@
         <v>45841</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52679,7 +52680,7 @@
         <v>45841</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52752,7 +52753,7 @@
         <v>45846</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52825,7 +52826,7 @@
         <v>45784</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52898,7 +52899,7 @@
         <v>45663</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52971,7 +52972,7 @@
         <v>45691</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53044,7 +53045,7 @@
         <v>45600</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53117,7 +53118,7 @@
         <v>45856</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53190,7 +53191,7 @@
         <v>45862</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53263,7 +53264,7 @@
         <v>45866</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53336,7 +53337,7 @@
         <v>45866</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53409,7 +53410,7 @@
         <v>45868</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53482,7 +53483,7 @@
         <v>45880</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53555,7 +53556,7 @@
         <v>45400</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53628,7 +53629,7 @@
         <v>44658</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53701,7 +53702,7 @@
         <v>44854</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53774,7 +53775,7 @@
         <v>44771</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53847,7 +53848,7 @@
         <v>45169</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53920,7 +53921,7 @@
         <v>44747</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53993,7 +53994,7 @@
         <v>44960</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54066,7 +54067,7 @@
         <v>44503</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54139,7 +54140,7 @@
         <v>45714</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54212,7 +54213,7 @@
         <v>45171</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54285,7 +54286,7 @@
         <v>46066</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>44690</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>45357</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>46083</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>46097</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>46083</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44585</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45561</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46097</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>46097</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44872</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>44879</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45603</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45675</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45351</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>45134</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45086</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44512</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45621</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45895</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44768</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>46001</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45236</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>45568</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>46109</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>44553</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>46217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>46223</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44971</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>46294</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45231</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45779</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45806</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45806</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>45264</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45876</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45351</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44861</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44533</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44531</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44655</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44858</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44533</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44497</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>44882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44552</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44506</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44732</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44657</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44776</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44655</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44852</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44733</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44656</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44594</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44750</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44509</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44868</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44663</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44882</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44621</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>44606</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44524</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44609</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44593</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44638</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44880</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44760</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44772</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>44945</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45412</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45180</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45348</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44959</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45553</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44881</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45585</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45681</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>44831</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>44512</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>45162</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45607</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>45162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45357</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44959</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45211</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45602</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44724</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44895</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44697</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>45344</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45124</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44894</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44578</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45006</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>45314</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>45237</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45201</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45247</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45558</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45321</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45376</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45357</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45363</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>45691</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45606</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44959</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45265</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45070</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45181</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45227</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44916</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44916</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45140</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45482</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45071</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45362</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>45224</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45411</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45334</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>44566</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44929</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>44824</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45518</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45399</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45603</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44517</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>45666</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45621</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>45180</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>45196</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45281</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45443</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45467</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44970</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>44971</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45683</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45664</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45246</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45685</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45299</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45157</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45606</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45324</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44947</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45227</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45227</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44636</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44873</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45412</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44800</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45259</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45231</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45608</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45663</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44663</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44503</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44663</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45075</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44606</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44607</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44607</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>44558</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45258</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45194</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45282</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45002</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45553</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45553</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>45281</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>45281</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45281</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45239</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18195,7 +18195,7 @@
         <v>45343</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45191</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45659</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45341</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45361</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45735</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45992</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45797</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45159</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45112</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45593</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45895</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45582</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45427</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45889</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45324</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45324</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45889</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45795</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45835</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45889</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45895</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45895</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45643</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44638</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45896</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45896</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45924</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45636</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45826</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45231</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45162</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44894</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45252</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>46101</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>45354</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45771</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45233</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45085</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45085</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45484</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45343</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45089</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>44636</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45905</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46140</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45187</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45611</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45909</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45362</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45043</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45742</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45547</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45547</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45075</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44945</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>46146</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45035</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45918</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>45091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45320</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45922</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45922</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45134</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45923</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>44911</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23866,7 +23866,7 @@
         <v>45926</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24012,7 +24012,7 @@
         <v>45933</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45933</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45934</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45934</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45934</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45934</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>46150</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45173</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45937</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45261</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45939</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45411</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45411</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>45938</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45938</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>44656</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>44881</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>45244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44762</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>45104</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25618,7 +25618,7 @@
         <v>44514</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>45203</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45947</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>45237</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45677</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45951</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45087</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45258</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45951</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45578</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45954</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45415</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45710</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45954</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45344</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>44678</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45474</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45959</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45960</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45086</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45960</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45960</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>44944</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45960</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45008</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45966</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45966</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45605</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45237</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45006</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>45968</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45974</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45975</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44971</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45974</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>44781</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45626</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45626</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45666</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45236</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45236</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45194</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45140</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45140</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45140</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45607</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>44809</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29351,7 +29351,7 @@
         <v>45281</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45189</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45097</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45273</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>44638</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45686</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45988</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45395</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45992</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>46168</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45163</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45560</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45994</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>45994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30378,7 +30378,7 @@
         <v>45994</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30451,7 +30451,7 @@
         <v>45994</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30524,7 +30524,7 @@
         <v>45994</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45994</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45698</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45996</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46001</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45533</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45223</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>46001</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45140</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45603</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45626</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>46125</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46009</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45691</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>44626</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45691</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45771</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45698</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44914</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>45715</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>45726</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>45688</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>45699</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45701</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>45603</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45603</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45043</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45398</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>44971</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>44515</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45199</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46029</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>45071</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45427</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45166</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>44830</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45691</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>46030</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>46030</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46041</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>46177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46182</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>46182</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45356</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45601</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>46049</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46048</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>46048</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45280</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45498</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45197</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45316</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45357</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46055</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45009</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45163</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>44530</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>46181</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45407</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45471</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44847</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>46062</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>44812</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44971</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45601</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44685</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>46071</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46071</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>45538</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45093</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45320</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46077</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>46063</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>46063</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>46063</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44771</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45215</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>46190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>44817</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45070</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46087</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45671</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>46091</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45002</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45484</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46191</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45225</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45625</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45140</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45120</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>46101</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45166</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45166</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45166</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>46112</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44959</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>44959</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46114</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46118</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>44882</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45072</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>46121</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46125</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>44845</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45338</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>46128</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>46128</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45395</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>45676</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>45385</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45626</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>45626</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>45626</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>45299</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45320</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45224</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45363</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>45166</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45225</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45190</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>44501</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45947</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>45384</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>45163</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45558</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45597</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45565</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45225</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45225</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45250</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45775</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>45104</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45008</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40575,7 +40575,7 @@
         <v>44763</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>45328</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>46206</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45086</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45552</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40940,7 +40940,7 @@
         <v>45552</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41013,7 +41013,7 @@
         <v>46211</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>46216</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46216</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46216</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>46211</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45139</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45408</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>46223</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>44735</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>46223</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>46224</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>46224</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>46223</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41972,7 +41972,7 @@
         <v>46224</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>46227</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42123,7 +42123,7 @@
         <v>46272</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45379</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>46272</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45461</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>46272</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45573</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>46271</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>46271</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45033</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45934</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45161</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>46135</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>46231</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45377</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45377</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45377</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>46232</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>46274</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>46277</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>46277</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44858</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45363</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45474</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45590</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45573</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45227</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45187</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45257</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>46238</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45691</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45408</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>46240</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45332</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45134</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>44593</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45242</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45939</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46277</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>44810</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45427</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45043,7 +45043,7 @@
         <v>45246</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>45098</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45272</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45086</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         <v>44565</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>46245</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>45604</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45070</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>44642</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45598</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45773,7 +45773,7 @@
         <v>46248</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45846,7 +45846,7 @@
         <v>45273</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45919,7 +45919,7 @@
         <v>46057</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45059</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45059</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46138,7 +46138,7 @@
         <v>46293</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45168</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46284,7 +46284,7 @@
         <v>45168</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45038</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>46293</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>44909</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>45750</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46649,7 +46649,7 @@
         <v>45745</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>46293</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>46247</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45225</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>44967</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>44967</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>45643</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>45041</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>44497</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45090</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>44672</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45209</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>46294</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>44613</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45544</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45158</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>45428</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45070</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45471</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45939</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>44658</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>44488</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>46297</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>46297</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>46253</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>46297</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45015</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45071</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46300</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45898</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>46300</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>46300</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>45231</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>46255</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49146,7 +49146,7 @@
         <v>45782</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>46255</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49292,7 +49292,7 @@
         <v>45785</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>45412</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>46255</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>46255</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45784</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>46300</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49735,7 +49735,7 @@
         <v>45709</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45157</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45791</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49954,7 +49954,7 @@
         <v>45790</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>46261</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>46262</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>46261</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>46261</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45797</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>45799</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50465,7 +50465,7 @@
         <v>45806</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45806</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>45806</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45132</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45473</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>46268</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>46267</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45212</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45824</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>45727</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>45727</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45826</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45730</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45743</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45720</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>45833</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>45835</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45835</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45833</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45835</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>45835</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45835</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45838</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>45838</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52222,7 +52222,7 @@
         <v>45838</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45838</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52378,7 +52378,7 @@
         <v>45838</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52456,7 +52456,7 @@
         <v>45838</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45838</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45841</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45841</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45846</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45784</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>45663</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>45691</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45600</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45856</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45862</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>45866</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45866</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45868</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45880</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45400</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44658</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>44854</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>44771</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45169</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>44747</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>44960</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>44503</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>45714</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45171</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         <v>46066</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46097</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45357</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>46083</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44585</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45561</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46097</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>46097</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44872</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45264</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44768</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>46217</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>46001</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45231</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45779</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>46073</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>46097</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46109</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>44553</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45876</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45385</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45086</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45299</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45236</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45134</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45675</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45568</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45351</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44861</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44533</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44531</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44655</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44868</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44533</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44497</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>44882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44552</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>44506</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44732</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44657</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44776</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44655</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44733</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44509</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44868</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44663</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44882</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>44524</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44609</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44593</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44638</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44624</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44880</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44497</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45626</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>45626</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45607</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45471</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45344</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45795</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45215</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45889</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44781</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45395</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45889</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45139</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>44896</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45091</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>45896</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44887</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44894</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>45362</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45552</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45361</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45636</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>45771</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45075</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45407</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45162</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45905</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44760</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45909</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45625</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44514</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45601</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45071</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45918</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45104</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45320</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45565</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45922</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45922</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45923</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44517</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45196</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44613</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45926</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45120</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>46168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45237</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44771</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45085</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>46125</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45771</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45357</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45258</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45933</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45934</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45934</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45246</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45934</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45933</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45934</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45597</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44512</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44971</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45939</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45093</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45398</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45250</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45428</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>45939</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>46177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>45376</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45474</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45443</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>44809</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45415</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>44916</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>44916</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>45242</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45086</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45482</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45518</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45951</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46181</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45582</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>45951</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45683</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>46182</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46182</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45775</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45954</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45006</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45960</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45960</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45959</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45960</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45960</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45321</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45002</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45227</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45227</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45124</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45140</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45608</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>44970</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45363</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45224</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45966</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45966</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>46190</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45412</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45265</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45265</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45320</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45968</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45209</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44800</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45181</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45356</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45975</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>44929</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45671</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45273</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45261</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45735</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45281</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45408</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45070</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45677</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45379</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45357</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45259</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45578</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45629</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45603</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45408</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45992</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46206</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45467</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45320</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45994</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45994</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45994</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45258</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45332</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45996</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45072</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45604</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>46216</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46216</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>46216</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45593</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>46223</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46001</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46223</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46223</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45231</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>46001</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>46224</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46224</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46224</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46227</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45782</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45934</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46231</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46135</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45784</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46232</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45412</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>46277</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46277</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45785</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45701</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45691</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45715</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45698</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45699</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45603</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45603</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45688</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45691</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45726</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45043</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45709</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46238</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45790</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46029</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46030</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>46030</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45157</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46277</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46240</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46041</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46245</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45797</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46048</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45939</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46049</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45799</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>46247</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45806</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45806</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45806</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>46055</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>46057</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45598</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45334</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45473</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45132</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>46248</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>46293</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>46294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>46293</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>46071</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46071</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45824</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46077</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45484</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46063</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>46063</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45484</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>46063</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45826</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45720</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45743</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45730</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45727</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46253</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45727</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46087</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46297</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45833</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46300</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45838</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46255</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45835</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45835</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45835</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46297</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45838</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46300</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45835</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45838</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45835</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45838</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>46300</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45838</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45838</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45898</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44895</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46297</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>46255</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>46255</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>46255</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44914</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45841</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45841</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45939</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45846</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>46101</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45273</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45341</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>46300</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45784</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45605</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45663</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45691</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45856</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45600</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45862</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46112</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45866</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46261</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46114</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45866</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44873</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45868</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>46118</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46121</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>46261</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46125</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44656</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45880</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46128</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>46262</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46128</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45498</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45626</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45159</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45097</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>44909</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
         <v>45362</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45924</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45354</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45558</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45895</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45553</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45553</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44638</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45343</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44626</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46267</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45348</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>44881</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45947</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44971</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44501</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>44672</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>46271</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46140</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>46271</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45041</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45231</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45835</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45826</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>46272</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45797</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>46272</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46272</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45992</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45573</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45385</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46101</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45324</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45324</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45343</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45547</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45547</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45547</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44945</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>44663</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44724</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45244</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46146</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>46274</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45070</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46150</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44959</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>44959</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44959</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45427</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45553</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>44735</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45070</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>44911</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45411</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>44831</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45961</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44908</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45225</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45225</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>45299</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44965</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45314</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>44971</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>45611</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45602</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45411</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45411</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45474</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>44503</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45006</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45140</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45664</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45666</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45035</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45573</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45158</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45606</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>44812</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45225</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45691</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45691</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44565</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45161</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45043</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44810</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45224</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45299</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45237</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45070</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45223</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45686</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45140</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45008</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45134</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45180</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>44530</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45033</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45538</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45601</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45090</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>44882</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44917</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45252</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45086</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44858</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45093</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45395</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45239</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45104</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45104</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45203</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45590</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45071</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>44959</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>45112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45075</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45663</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45015</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>44697</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>44944</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>44578</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45168</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45168</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45162</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45750</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45363</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>45162</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>44947</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>44959</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>44971</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45157</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45338</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>45134</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45180</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45086</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45643</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45227</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45399</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45187</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45043</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45324</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45162</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45163</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45162</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>45659</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45585</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45621</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45607</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45059</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>45059</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>44663</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45377</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45377</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45377</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45471</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45558</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>44558</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45191</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45328</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>44607</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>44607</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45281</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44763</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45412</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45603</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47691,7 +47691,7 @@
         <v>45316</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45225</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>45181</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45344</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45173</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45166</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45201</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45194</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45194</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45166</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45166</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>44642</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45166</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44638</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44638</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45231</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45691</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45199</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45187</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45560</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45427</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45098</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45427</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45666</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45676</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45166</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45710</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45140</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>45140</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45140</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>44845</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>44658</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45626</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45626</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45626</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45233</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45681</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>45363</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>45236</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45236</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45197</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>45244</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>45211</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45685</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>44685</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45162</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>44824</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45282</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45189</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45239</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45247</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>45461</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51580,7 +51580,7 @@
         <v>45227</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>44847</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>44593</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>44772</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45257</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45237</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45357</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45038</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45087</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45745</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45245</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45281</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45281</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45281</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45257</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>44515</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45258</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45606</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>44830</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>44606</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>44566</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45008</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45384</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44762</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44678</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>44658</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45400</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>44854</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44771</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45169</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>44747</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>44960</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>44503</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45714</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45171</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46066</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>

--- a/Översikt ULRICEHAMN.xlsx
+++ b/Översikt ULRICEHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45147</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>46083</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>46097</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>44690</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>45357</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>46083</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>44585</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45561</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>46097</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45785</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>46097</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>44872</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45264</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44879</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>44768</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>46217</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>46001</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45231</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45779</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45806</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45806</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>46073</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>46294</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>46097</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>46109</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>44553</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45876</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>44971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>45385</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>45086</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45299</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45351</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45236</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>45603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45134</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>45675</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45568</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45351</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>44861</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>44679</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44533</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44531</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>44817</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44655</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44868</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44809</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>44823</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>44533</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44713</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44497</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>44882</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44552</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>44506</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44732</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44657</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44543</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>44854</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>44776</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44655</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>44775</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44852</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>44733</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44594</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>44532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44509</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>44868</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>44663</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44882</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>44524</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44609</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44593</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44638</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44624</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>44880</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>44497</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45626</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>45626</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45607</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45471</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45344</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45795</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45215</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45889</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44781</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45395</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45889</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45139</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>44896</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45091</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45246</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>45896</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45895</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45895</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44887</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44894</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>45362</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>45552</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45552</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45361</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45636</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>45771</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45075</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45407</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45162</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45905</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44760</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45909</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45625</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44514</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45601</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45071</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45698</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45918</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45104</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45320</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45565</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45922</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45922</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45923</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44517</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45196</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44613</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45926</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>45120</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>46168</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45237</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44771</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45926</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44636</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45085</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>46125</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45771</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45357</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45258</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45933</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45934</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45934</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45246</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45934</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45163</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45933</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45934</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45597</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45937</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44512</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44971</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45939</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45153</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>45093</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45398</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45250</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45428</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>45939</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45002</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>46177</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>45376</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45474</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45443</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>44809</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45415</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>44916</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>44916</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>45242</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45086</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45482</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45518</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45951</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46181</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>45582</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>45951</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45683</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>46182</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46182</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45775</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45954</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45954</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45006</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45960</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45960</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45959</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45960</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45960</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45321</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45002</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>45227</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>45227</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45124</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>45140</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45608</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>44970</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45363</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44636</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45224</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46191</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45966</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45966</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>46190</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45412</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45265</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45265</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45320</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45968</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45209</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>44800</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45181</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>45356</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45974</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45163</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45975</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>44929</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45671</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45273</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45261</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45280</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45735</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45281</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45408</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45070</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45677</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45379</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45357</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45259</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45578</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45629</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45603</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45408</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45992</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>46206</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45994</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45467</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45320</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45994</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45994</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45994</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45258</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45332</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45996</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45072</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45604</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>46216</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46216</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>46216</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45593</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45999</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>46223</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46001</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46223</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>46223</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45231</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>46001</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>46224</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>46224</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>46224</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>46227</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>45782</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45934</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46231</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46135</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45784</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46232</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45412</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>46277</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>46277</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45785</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46009</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45701</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45691</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45715</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45698</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45699</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45603</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45603</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45688</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45691</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45726</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45043</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45709</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46238</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45790</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46029</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46030</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>46030</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>45157</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46277</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46240</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46041</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46245</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45797</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46048</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45939</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>46048</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>46049</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45799</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>46247</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45806</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45806</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45806</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>46055</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>46057</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45598</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45334</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45473</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45132</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>46248</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>46293</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>46294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>46293</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46293</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>46071</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46071</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45824</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46077</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45484</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46063</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>46063</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45484</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>46063</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45826</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45720</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45743</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45730</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45727</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46253</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45727</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46087</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46297</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45833</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46300</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45833</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45838</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46255</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45835</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45835</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45835</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>46297</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45838</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46300</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45835</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45838</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>45835</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>45838</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31682,7 +31682,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>46300</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>45838</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>45838</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45898</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44895</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>46297</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>46255</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>46255</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>46255</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44914</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32510,7 +32510,7 @@
         <v>45841</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>45841</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>45939</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45846</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>46101</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>45273</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45341</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>46300</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45784</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45605</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45663</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>45691</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45856</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>45600</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>45862</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46112</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45866</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46261</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46114</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>45866</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>44873</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45868</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>46118</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46121</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>46261</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46125</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>44656</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>46261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45880</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46128</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>46262</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46128</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45498</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45626</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45159</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45097</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>44909</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
         <v>45362</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45924</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45354</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45558</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45895</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45553</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45553</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44638</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>45343</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44626</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46267</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45348</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>44881</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45947</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44971</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44501</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>44672</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>46271</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46140</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>46271</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45041</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>45231</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45835</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45826</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>46272</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>45797</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>46272</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>46272</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45992</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45573</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45385</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46101</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45324</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45324</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45343</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45547</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45547</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>45547</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44945</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>44663</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44724</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45244</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46146</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>46274</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45070</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>46150</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44959</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38838,7 +38838,7 @@
         <v>44959</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44959</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45427</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>45553</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>44735</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>45070</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>44911</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45411</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>44831</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45961</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44908</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45225</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39714,7 +39714,7 @@
         <v>45225</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>45299</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44965</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39933,7 +39933,7 @@
         <v>45314</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>44971</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>45611</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45602</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45411</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45411</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45474</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>44503</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>45006</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45140</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45664</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40741,7 +40741,7 @@
         <v>45666</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45035</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45573</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45158</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45606</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>44812</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>45225</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45691</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45691</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41398,7 +41398,7 @@
         <v>44565</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41471,7 +41471,7 @@
         <v>45161</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45043</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>44810</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45224</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45299</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45237</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>45070</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45223</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45686</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45140</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45008</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45134</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42420,7 +42420,7 @@
         <v>45180</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>44530</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45033</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>45538</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45601</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45090</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>44882</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44917</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>45252</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45086</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>44858</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45093</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>45395</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45239</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45104</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45104</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45203</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45590</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45071</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>44959</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         <v>45112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45075</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45663</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45015</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>44697</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>44944</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>44578</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45168</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44469,7 +44469,7 @@
         <v>45168</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45162</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45750</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45363</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>45162</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>44947</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>44959</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>44971</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45157</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45338</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>45134</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45180</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>45086</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45643</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45227</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>45399</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45710,7 +45710,7 @@
         <v>45187</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45043</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45324</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45162</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45163</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45162</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>45659</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45585</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45621</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45607</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45059</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>45059</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>44663</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45377</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46737,7 +46737,7 @@
         <v>45377</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45377</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45471</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45558</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>44558</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>45191</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45328</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>44607</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>44607</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>45281</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>44763</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45412</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45603</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47691,7 +47691,7 @@
         <v>45316</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47764,7 +47764,7 @@
         <v>45225</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47837,7 +47837,7 @@
         <v>45181</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>45344</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45173</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45166</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45201</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45194</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>45194</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>45166</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45166</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>44642</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45166</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>44638</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44638</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45231</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>45691</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45199</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45187</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>45560</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45427</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49239,7 +49239,7 @@
         <v>45098</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49312,7 +49312,7 @@
         <v>45427</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>45666</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45676</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45166</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>45710</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45140</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>45140</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45140</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49896,7 +49896,7 @@
         <v>44845</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49969,7 +49969,7 @@
         <v>44658</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50042,7 +50042,7 @@
         <v>45626</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45626</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50188,7 +50188,7 @@
         <v>45626</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>45233</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45681</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
         <v>45363</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50480,7 +50480,7 @@
         <v>45236</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>45236</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45197</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50704,7 +50704,7 @@
         <v>45244</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50777,7 +50777,7 @@
         <v>45211</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45685</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50923,7 +50923,7 @@
         <v>44685</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50996,7 +50996,7 @@
         <v>45162</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>44824</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45282</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45189</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45239</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45247</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>45461</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
         <v>45190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51580,7 +51580,7 @@
         <v>45227</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51653,7 +51653,7 @@
         <v>44847</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51726,7 +51726,7 @@
         <v>44593</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>44772</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>45257</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45237</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45357</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>45038</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45087</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>45745</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>45245</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45281</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52461,7 +52461,7 @@
         <v>45281</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45281</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45257</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>44515</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45258</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>45606</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52899,7 +52899,7 @@
         <v>44830</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52972,7 +52972,7 @@
         <v>44606</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>44566</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53118,7 +53118,7 @@
         <v>45008</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53191,7 +53191,7 @@
         <v>45384</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>44762</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44678</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>44658</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45400</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>44854</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44771</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>45169</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>44747</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>44960</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53921,7 +53921,7 @@
         <v>44503</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53994,7 +53994,7 @@
         <v>45714</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45171</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54140,7 +54140,7 @@
         <v>46066</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
